--- a/Programa conferencia.xlsx
+++ b/Programa conferencia.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Apoio1\Desktop\Sistema Conferencia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Apoio1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F013A7F-475E-481C-B347-EE10346E022C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D6364EF-C220-48C6-9C2A-A772A520803A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="390" windowWidth="20490" windowHeight="11070" xr2:uid="{D9876C19-AA45-4750-98F6-B6407576DC16}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{D9876C19-AA45-4750-98F6-B6407576DC16}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="124">
   <si>
     <t>Código do Produto</t>
   </si>
@@ -53,76 +53,367 @@
     <t>Volumes</t>
   </si>
   <si>
-    <t>7891033906130</t>
-  </si>
-  <si>
-    <t>7891033941339</t>
-  </si>
-  <si>
-    <t>7891033941346</t>
-  </si>
-  <si>
-    <t>7891033941360</t>
-  </si>
-  <si>
-    <t>7891033941384</t>
-  </si>
-  <si>
-    <t>7891033941391</t>
-  </si>
-  <si>
-    <t>7891033941407</t>
-  </si>
-  <si>
-    <t>7891033941414</t>
-  </si>
-  <si>
-    <t>7891033941452</t>
-  </si>
-  <si>
-    <t>7891033941476</t>
-  </si>
-  <si>
-    <t>7891033941483</t>
-  </si>
-  <si>
-    <t>7891033941490</t>
-  </si>
-  <si>
-    <t>7891033941544</t>
-  </si>
-  <si>
-    <t>7891033941568</t>
-  </si>
-  <si>
-    <t>7891033941575</t>
-  </si>
-  <si>
-    <t>7891033941582</t>
-  </si>
-  <si>
-    <t>7891033941599</t>
-  </si>
-  <si>
-    <t>7891033941612</t>
-  </si>
-  <si>
-    <t>7891033941629</t>
-  </si>
-  <si>
-    <t>7891033943050</t>
-  </si>
-  <si>
-    <t>7891033943494</t>
-  </si>
-  <si>
-    <t>7891033945740</t>
-  </si>
-  <si>
-    <t>7891033945764</t>
-  </si>
-  <si>
-    <t>7891033949779</t>
+    <t>7891033013029</t>
+  </si>
+  <si>
+    <t>7891033013173</t>
+  </si>
+  <si>
+    <t>7891033016419</t>
+  </si>
+  <si>
+    <t>7891033197347</t>
+  </si>
+  <si>
+    <t>7891033301997</t>
+  </si>
+  <si>
+    <t>7891033473649</t>
+  </si>
+  <si>
+    <t>7891033474004</t>
+  </si>
+  <si>
+    <t>7891033476299</t>
+  </si>
+  <si>
+    <t>7891033476305</t>
+  </si>
+  <si>
+    <t>7891033478873</t>
+  </si>
+  <si>
+    <t>7891033479085</t>
+  </si>
+  <si>
+    <t>7891033482801</t>
+  </si>
+  <si>
+    <t>7891033483037</t>
+  </si>
+  <si>
+    <t>7891033483150</t>
+  </si>
+  <si>
+    <t>7891033483181</t>
+  </si>
+  <si>
+    <t>7891033486342</t>
+  </si>
+  <si>
+    <t>7891033486649</t>
+  </si>
+  <si>
+    <t>7891033487905</t>
+  </si>
+  <si>
+    <t>7891033492459</t>
+  </si>
+  <si>
+    <t>7891033492503</t>
+  </si>
+  <si>
+    <t>7891033492527</t>
+  </si>
+  <si>
+    <t>7891033497652</t>
+  </si>
+  <si>
+    <t>7891033500222</t>
+  </si>
+  <si>
+    <t>7891033506774</t>
+  </si>
+  <si>
+    <t>7891033508815</t>
+  </si>
+  <si>
+    <t>7891033509317</t>
+  </si>
+  <si>
+    <t>7891033511471</t>
+  </si>
+  <si>
+    <t>7891033517459</t>
+  </si>
+  <si>
+    <t>7891033517466</t>
+  </si>
+  <si>
+    <t>7891033517497</t>
+  </si>
+  <si>
+    <t>7891033520190</t>
+  </si>
+  <si>
+    <t>7891033520220</t>
+  </si>
+  <si>
+    <t>7891033520237</t>
+  </si>
+  <si>
+    <t>7891033522163</t>
+  </si>
+  <si>
+    <t>7891033525072</t>
+  </si>
+  <si>
+    <t>7891033530946</t>
+  </si>
+  <si>
+    <t>7891033530953</t>
+  </si>
+  <si>
+    <t>7891033533558</t>
+  </si>
+  <si>
+    <t>7891033534357</t>
+  </si>
+  <si>
+    <t>7891033534364</t>
+  </si>
+  <si>
+    <t>7891033534692</t>
+  </si>
+  <si>
+    <t>7891033535187</t>
+  </si>
+  <si>
+    <t>7891033535194</t>
+  </si>
+  <si>
+    <t>7891033538355</t>
+  </si>
+  <si>
+    <t>7891033548873</t>
+  </si>
+  <si>
+    <t>7891033550838</t>
+  </si>
+  <si>
+    <t>7891033552955</t>
+  </si>
+  <si>
+    <t>7891033556694</t>
+  </si>
+  <si>
+    <t>7891033558049</t>
+  </si>
+  <si>
+    <t>7891033574919</t>
+  </si>
+  <si>
+    <t>7891033595556</t>
+  </si>
+  <si>
+    <t>7891033595839</t>
+  </si>
+  <si>
+    <t>7891033706686</t>
+  </si>
+  <si>
+    <t>7891033757718</t>
+  </si>
+  <si>
+    <t>7891033766215</t>
+  </si>
+  <si>
+    <t>7891033779901</t>
+  </si>
+  <si>
+    <t>7891033808496</t>
+  </si>
+  <si>
+    <t>7891033820603</t>
+  </si>
+  <si>
+    <t>7891033820924</t>
+  </si>
+  <si>
+    <t>7891033826858</t>
+  </si>
+  <si>
+    <t>7891033826865</t>
+  </si>
+  <si>
+    <t>7891033826889</t>
+  </si>
+  <si>
+    <t>7891033826896</t>
+  </si>
+  <si>
+    <t>7891033838233</t>
+  </si>
+  <si>
+    <t>7891033839711</t>
+  </si>
+  <si>
+    <t>7891033841820</t>
+  </si>
+  <si>
+    <t>7891033842131</t>
+  </si>
+  <si>
+    <t>7891033842148</t>
+  </si>
+  <si>
+    <t>7891033843855</t>
+  </si>
+  <si>
+    <t>7891033843909</t>
+  </si>
+  <si>
+    <t>7891033853694</t>
+  </si>
+  <si>
+    <t>7891033856558</t>
+  </si>
+  <si>
+    <t>7891033857968</t>
+  </si>
+  <si>
+    <t>7891033858453</t>
+  </si>
+  <si>
+    <t>7891033859351</t>
+  </si>
+  <si>
+    <t>7891033862061</t>
+  </si>
+  <si>
+    <t>7891033864652</t>
+  </si>
+  <si>
+    <t>7891033870134</t>
+  </si>
+  <si>
+    <t>7891033871261</t>
+  </si>
+  <si>
+    <t>7891033871285</t>
+  </si>
+  <si>
+    <t>7891033871315</t>
+  </si>
+  <si>
+    <t>7891033871353</t>
+  </si>
+  <si>
+    <t>7891033871438</t>
+  </si>
+  <si>
+    <t>7891033872725</t>
+  </si>
+  <si>
+    <t>7891033872923</t>
+  </si>
+  <si>
+    <t>7891033875320</t>
+  </si>
+  <si>
+    <t>7891033878963</t>
+  </si>
+  <si>
+    <t>7891033878987</t>
+  </si>
+  <si>
+    <t>7891033879724</t>
+  </si>
+  <si>
+    <t>7891033880652</t>
+  </si>
+  <si>
+    <t>7891033882038</t>
+  </si>
+  <si>
+    <t>7891033883646</t>
+  </si>
+  <si>
+    <t>7891033885060</t>
+  </si>
+  <si>
+    <t>7891033885077</t>
+  </si>
+  <si>
+    <t>7891033885084</t>
+  </si>
+  <si>
+    <t>7891033885091</t>
+  </si>
+  <si>
+    <t>7891033885107</t>
+  </si>
+  <si>
+    <t>7891033888979</t>
+  </si>
+  <si>
+    <t>7891033896370</t>
+  </si>
+  <si>
+    <t>7891033896783</t>
+  </si>
+  <si>
+    <t>7891033896790</t>
+  </si>
+  <si>
+    <t>7891033896806</t>
+  </si>
+  <si>
+    <t>7891033898169</t>
+  </si>
+  <si>
+    <t>7891033903108</t>
+  </si>
+  <si>
+    <t>7891033905133</t>
+  </si>
+  <si>
+    <t>7891033908134</t>
+  </si>
+  <si>
+    <t>7891033917211</t>
+  </si>
+  <si>
+    <t>7891033930470</t>
+  </si>
+  <si>
+    <t>7891033930623</t>
+  </si>
+  <si>
+    <t>7891033935413</t>
+  </si>
+  <si>
+    <t>7891033941995</t>
+  </si>
+  <si>
+    <t>7891033947584</t>
+  </si>
+  <si>
+    <t>7891033948161</t>
+  </si>
+  <si>
+    <t>7891033958306</t>
+  </si>
+  <si>
+    <t>7891033962945</t>
+  </si>
+  <si>
+    <t>7891033963713</t>
+  </si>
+  <si>
+    <t>7891033963720</t>
+  </si>
+  <si>
+    <t>7891033963737</t>
+  </si>
+  <si>
+    <t>7891033973811</t>
+  </si>
+  <si>
+    <t>7891033973842</t>
+  </si>
+  <si>
+    <t>7891033977239</t>
   </si>
 </sst>
 </file>
@@ -494,7 +785,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14B8BA79-486A-4311-9DC6-50AF49FF2C77}">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C122"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
@@ -513,266 +804,1333 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>90613</v>
+        <v>1302</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>94133</v>
+        <v>1317</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
       <c r="C3">
-        <v>51</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>94134</v>
+        <v>1641</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
       <c r="C4">
-        <v>51</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>94136</v>
+        <v>19734</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
       </c>
       <c r="C5">
-        <v>64</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>94138</v>
+        <v>30199</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
       </c>
       <c r="C6">
-        <v>49</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>94139</v>
+        <v>47364</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
       </c>
       <c r="C7">
-        <v>110</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>94140</v>
+        <v>47400</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
       </c>
       <c r="C8">
-        <v>49</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>94141</v>
+        <v>47629</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
       </c>
       <c r="C9">
-        <v>30</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>94145</v>
+        <v>47630</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
       </c>
       <c r="C10">
-        <v>114</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>94147</v>
+        <v>47887</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
       </c>
       <c r="C11">
-        <v>83</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>94148</v>
+        <v>47908</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
       </c>
       <c r="C12">
-        <v>87</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>94149</v>
+        <v>48280</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
       </c>
       <c r="C13">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>94154</v>
+        <v>48303</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
       </c>
       <c r="C14">
-        <v>88</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>94156</v>
+        <v>48315</v>
       </c>
       <c r="B15" t="s">
         <v>16</v>
       </c>
       <c r="C15">
-        <v>22</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>94157</v>
+        <v>48318</v>
       </c>
       <c r="B16" t="s">
         <v>17</v>
       </c>
       <c r="C16">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>94158</v>
+        <v>48634</v>
       </c>
       <c r="B17" t="s">
         <v>18</v>
       </c>
       <c r="C17">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>94159</v>
+        <v>48664</v>
       </c>
       <c r="B18" t="s">
         <v>19</v>
       </c>
       <c r="C18">
-        <v>154</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>94161</v>
+        <v>48790</v>
       </c>
       <c r="B19" t="s">
         <v>20</v>
       </c>
       <c r="C19">
-        <v>46</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>94162</v>
+        <v>49245</v>
       </c>
       <c r="B20" t="s">
         <v>21</v>
       </c>
       <c r="C20">
-        <v>86</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>94305</v>
+        <v>49250</v>
       </c>
       <c r="B21" t="s">
         <v>22</v>
       </c>
       <c r="C21">
-        <v>52</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>94349</v>
+        <v>49252</v>
       </c>
       <c r="B22" t="s">
         <v>23</v>
       </c>
       <c r="C22">
-        <v>134</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>94574</v>
+        <v>49765</v>
       </c>
       <c r="B23" t="s">
         <v>24</v>
       </c>
       <c r="C23">
-        <v>53</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>94576</v>
+        <v>50022</v>
       </c>
       <c r="B24" t="s">
         <v>25</v>
       </c>
       <c r="C24">
-        <v>155</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>94977</v>
+        <v>50677</v>
       </c>
       <c r="B25" t="s">
         <v>26</v>
       </c>
       <c r="C25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>50881</v>
+      </c>
+      <c r="B26" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>50931</v>
+      </c>
+      <c r="B27" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>51147</v>
+      </c>
+      <c r="B28" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>51745</v>
+      </c>
+      <c r="B29" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>51746</v>
+      </c>
+      <c r="B30" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>51749</v>
+      </c>
+      <c r="B31" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>52019</v>
+      </c>
+      <c r="B32" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>52022</v>
+      </c>
+      <c r="B33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33">
         <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>52023</v>
+      </c>
+      <c r="B34" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>52216</v>
+      </c>
+      <c r="B35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>52507</v>
+      </c>
+      <c r="B36" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>53094</v>
+      </c>
+      <c r="B37" t="s">
+        <v>38</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>53095</v>
+      </c>
+      <c r="B38" t="s">
+        <v>39</v>
+      </c>
+      <c r="C38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>53355</v>
+      </c>
+      <c r="B39" t="s">
+        <v>40</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>53435</v>
+      </c>
+      <c r="B40" t="s">
+        <v>41</v>
+      </c>
+      <c r="C40">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>53436</v>
+      </c>
+      <c r="B41" t="s">
+        <v>42</v>
+      </c>
+      <c r="C41">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>53469</v>
+      </c>
+      <c r="B42" t="s">
+        <v>43</v>
+      </c>
+      <c r="C42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>53518</v>
+      </c>
+      <c r="B43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>53519</v>
+      </c>
+      <c r="B44" t="s">
+        <v>45</v>
+      </c>
+      <c r="C44">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>53835</v>
+      </c>
+      <c r="B45" t="s">
+        <v>46</v>
+      </c>
+      <c r="C45">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>54887</v>
+      </c>
+      <c r="B46" t="s">
+        <v>47</v>
+      </c>
+      <c r="C46">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>55083</v>
+      </c>
+      <c r="B47" t="s">
+        <v>48</v>
+      </c>
+      <c r="C47">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>55295</v>
+      </c>
+      <c r="B48" t="s">
+        <v>49</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>55669</v>
+      </c>
+      <c r="B49" t="s">
+        <v>50</v>
+      </c>
+      <c r="C49">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>55804</v>
+      </c>
+      <c r="B50" t="s">
+        <v>51</v>
+      </c>
+      <c r="C50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>57491</v>
+      </c>
+      <c r="B51" t="s">
+        <v>52</v>
+      </c>
+      <c r="C51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>59555</v>
+      </c>
+      <c r="B52" t="s">
+        <v>53</v>
+      </c>
+      <c r="C52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>59583</v>
+      </c>
+      <c r="B53" t="s">
+        <v>54</v>
+      </c>
+      <c r="C53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>70668</v>
+      </c>
+      <c r="B54" t="s">
+        <v>55</v>
+      </c>
+      <c r="C54">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>75771</v>
+      </c>
+      <c r="B55" t="s">
+        <v>56</v>
+      </c>
+      <c r="C55">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>76621</v>
+      </c>
+      <c r="B56" t="s">
+        <v>57</v>
+      </c>
+      <c r="C56">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>77990</v>
+      </c>
+      <c r="B57" t="s">
+        <v>58</v>
+      </c>
+      <c r="C57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>80849</v>
+      </c>
+      <c r="B58" t="s">
+        <v>59</v>
+      </c>
+      <c r="C58">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>82060</v>
+      </c>
+      <c r="B59" t="s">
+        <v>60</v>
+      </c>
+      <c r="C59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>82092</v>
+      </c>
+      <c r="B60" t="s">
+        <v>61</v>
+      </c>
+      <c r="C60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>82685</v>
+      </c>
+      <c r="B61" t="s">
+        <v>62</v>
+      </c>
+      <c r="C61">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>82686</v>
+      </c>
+      <c r="B62" t="s">
+        <v>63</v>
+      </c>
+      <c r="C62">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>82688</v>
+      </c>
+      <c r="B63" t="s">
+        <v>64</v>
+      </c>
+      <c r="C63">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>82689</v>
+      </c>
+      <c r="B64" t="s">
+        <v>65</v>
+      </c>
+      <c r="C64">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>83823</v>
+      </c>
+      <c r="B65" t="s">
+        <v>66</v>
+      </c>
+      <c r="C65">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>83971</v>
+      </c>
+      <c r="B66" t="s">
+        <v>67</v>
+      </c>
+      <c r="C66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>84182</v>
+      </c>
+      <c r="B67" t="s">
+        <v>68</v>
+      </c>
+      <c r="C67">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>84213</v>
+      </c>
+      <c r="B68" t="s">
+        <v>69</v>
+      </c>
+      <c r="C68">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>84214</v>
+      </c>
+      <c r="B69" t="s">
+        <v>70</v>
+      </c>
+      <c r="C69">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>84385</v>
+      </c>
+      <c r="B70" t="s">
+        <v>71</v>
+      </c>
+      <c r="C70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>84390</v>
+      </c>
+      <c r="B71" t="s">
+        <v>72</v>
+      </c>
+      <c r="C71">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>85369</v>
+      </c>
+      <c r="B72" t="s">
+        <v>73</v>
+      </c>
+      <c r="C72">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>85655</v>
+      </c>
+      <c r="B73" t="s">
+        <v>74</v>
+      </c>
+      <c r="C73">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>85796</v>
+      </c>
+      <c r="B74" t="s">
+        <v>75</v>
+      </c>
+      <c r="C74">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>85845</v>
+      </c>
+      <c r="B75" t="s">
+        <v>76</v>
+      </c>
+      <c r="C75">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>85935</v>
+      </c>
+      <c r="B76" t="s">
+        <v>77</v>
+      </c>
+      <c r="C76">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>86206</v>
+      </c>
+      <c r="B77" t="s">
+        <v>78</v>
+      </c>
+      <c r="C77">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>86465</v>
+      </c>
+      <c r="B78" t="s">
+        <v>79</v>
+      </c>
+      <c r="C78">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>87013</v>
+      </c>
+      <c r="B79" t="s">
+        <v>80</v>
+      </c>
+      <c r="C79">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>87126</v>
+      </c>
+      <c r="B80" t="s">
+        <v>81</v>
+      </c>
+      <c r="C80">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>87128</v>
+      </c>
+      <c r="B81" t="s">
+        <v>82</v>
+      </c>
+      <c r="C81">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>87131</v>
+      </c>
+      <c r="B82" t="s">
+        <v>83</v>
+      </c>
+      <c r="C82">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>87135</v>
+      </c>
+      <c r="B83" t="s">
+        <v>84</v>
+      </c>
+      <c r="C83">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>87143</v>
+      </c>
+      <c r="B84" t="s">
+        <v>85</v>
+      </c>
+      <c r="C84">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>87272</v>
+      </c>
+      <c r="B85" t="s">
+        <v>86</v>
+      </c>
+      <c r="C85">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>87292</v>
+      </c>
+      <c r="B86" t="s">
+        <v>87</v>
+      </c>
+      <c r="C86">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>87532</v>
+      </c>
+      <c r="B87" t="s">
+        <v>88</v>
+      </c>
+      <c r="C87">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>87896</v>
+      </c>
+      <c r="B88" t="s">
+        <v>89</v>
+      </c>
+      <c r="C88">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>87898</v>
+      </c>
+      <c r="B89" t="s">
+        <v>90</v>
+      </c>
+      <c r="C89">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>87972</v>
+      </c>
+      <c r="B90" t="s">
+        <v>91</v>
+      </c>
+      <c r="C90">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>88065</v>
+      </c>
+      <c r="B91" t="s">
+        <v>92</v>
+      </c>
+      <c r="C91">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>88203</v>
+      </c>
+      <c r="B92" t="s">
+        <v>93</v>
+      </c>
+      <c r="C92">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>88364</v>
+      </c>
+      <c r="B93" t="s">
+        <v>94</v>
+      </c>
+      <c r="C93">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>88506</v>
+      </c>
+      <c r="B94" t="s">
+        <v>95</v>
+      </c>
+      <c r="C94">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>88507</v>
+      </c>
+      <c r="B95" t="s">
+        <v>96</v>
+      </c>
+      <c r="C95">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>88508</v>
+      </c>
+      <c r="B96" t="s">
+        <v>97</v>
+      </c>
+      <c r="C96">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>88509</v>
+      </c>
+      <c r="B97" t="s">
+        <v>98</v>
+      </c>
+      <c r="C97">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>88510</v>
+      </c>
+      <c r="B98" t="s">
+        <v>99</v>
+      </c>
+      <c r="C98">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>88897</v>
+      </c>
+      <c r="B99" t="s">
+        <v>100</v>
+      </c>
+      <c r="C99">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>89637</v>
+      </c>
+      <c r="B100" t="s">
+        <v>101</v>
+      </c>
+      <c r="C100">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>89678</v>
+      </c>
+      <c r="B101" t="s">
+        <v>102</v>
+      </c>
+      <c r="C101">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>89679</v>
+      </c>
+      <c r="B102" t="s">
+        <v>103</v>
+      </c>
+      <c r="C102">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>89680</v>
+      </c>
+      <c r="B103" t="s">
+        <v>104</v>
+      </c>
+      <c r="C103">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>89816</v>
+      </c>
+      <c r="B104" t="s">
+        <v>105</v>
+      </c>
+      <c r="C104">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>90310</v>
+      </c>
+      <c r="B105" t="s">
+        <v>106</v>
+      </c>
+      <c r="C105">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>90513</v>
+      </c>
+      <c r="B106" t="s">
+        <v>107</v>
+      </c>
+      <c r="C106">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>90813</v>
+      </c>
+      <c r="B107" t="s">
+        <v>108</v>
+      </c>
+      <c r="C107">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>91721</v>
+      </c>
+      <c r="B108" t="s">
+        <v>109</v>
+      </c>
+      <c r="C108">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>93047</v>
+      </c>
+      <c r="B109" t="s">
+        <v>110</v>
+      </c>
+      <c r="C109">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>93062</v>
+      </c>
+      <c r="B110" t="s">
+        <v>111</v>
+      </c>
+      <c r="C110">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>93541</v>
+      </c>
+      <c r="B111" t="s">
+        <v>112</v>
+      </c>
+      <c r="C111">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>94199</v>
+      </c>
+      <c r="B112" t="s">
+        <v>113</v>
+      </c>
+      <c r="C112">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>94758</v>
+      </c>
+      <c r="B113" t="s">
+        <v>114</v>
+      </c>
+      <c r="C113">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>94816</v>
+      </c>
+      <c r="B114" t="s">
+        <v>115</v>
+      </c>
+      <c r="C114">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>95830</v>
+      </c>
+      <c r="B115" t="s">
+        <v>116</v>
+      </c>
+      <c r="C115">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>96294</v>
+      </c>
+      <c r="B116" t="s">
+        <v>117</v>
+      </c>
+      <c r="C116">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>96371</v>
+      </c>
+      <c r="B117" t="s">
+        <v>118</v>
+      </c>
+      <c r="C117">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>96372</v>
+      </c>
+      <c r="B118" t="s">
+        <v>119</v>
+      </c>
+      <c r="C118">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>96373</v>
+      </c>
+      <c r="B119" t="s">
+        <v>120</v>
+      </c>
+      <c r="C119">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>97381</v>
+      </c>
+      <c r="B120" t="s">
+        <v>121</v>
+      </c>
+      <c r="C120">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>97384</v>
+      </c>
+      <c r="B121" t="s">
+        <v>122</v>
+      </c>
+      <c r="C121">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>97723</v>
+      </c>
+      <c r="B122" t="s">
+        <v>123</v>
+      </c>
+      <c r="C122">
+        <v>210</v>
       </c>
     </row>
   </sheetData>

--- a/Programa conferencia.xlsx
+++ b/Programa conferencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Apoio1\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A056AEA2-4B69-4938-84AB-988D0B693837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0CFFA5D-869F-4B86-9C3A-0CCFD9C84C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{D9876C19-AA45-4750-98F6-B6407576DC16}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="166">
   <si>
     <t>Código do Produto</t>
   </si>
@@ -51,6 +51,495 @@
   </si>
   <si>
     <t>Volumes</t>
+  </si>
+  <si>
+    <t>7891033013029</t>
+  </si>
+  <si>
+    <t>7891033013142</t>
+  </si>
+  <si>
+    <t>7891033013173</t>
+  </si>
+  <si>
+    <t>7891033016440</t>
+  </si>
+  <si>
+    <t>7891033197347</t>
+  </si>
+  <si>
+    <t>7891033402205</t>
+  </si>
+  <si>
+    <t>7891033468980</t>
+  </si>
+  <si>
+    <t>7891033476299</t>
+  </si>
+  <si>
+    <t>7891033476305</t>
+  </si>
+  <si>
+    <t>7891033479085</t>
+  </si>
+  <si>
+    <t>7891033482801</t>
+  </si>
+  <si>
+    <t>7891033482962</t>
+  </si>
+  <si>
+    <t>7891033483150</t>
+  </si>
+  <si>
+    <t>7891033483754</t>
+  </si>
+  <si>
+    <t>7891033486649</t>
+  </si>
+  <si>
+    <t>7891033492503</t>
+  </si>
+  <si>
+    <t>7891033492527</t>
+  </si>
+  <si>
+    <t>7891033497652</t>
+  </si>
+  <si>
+    <t>7891033498123</t>
+  </si>
+  <si>
+    <t>7891033500123</t>
+  </si>
+  <si>
+    <t>7891033500147</t>
+  </si>
+  <si>
+    <t>7891033514410</t>
+  </si>
+  <si>
+    <t>7891033517459</t>
+  </si>
+  <si>
+    <t>7891033517466</t>
+  </si>
+  <si>
+    <t>7891033517497</t>
+  </si>
+  <si>
+    <t>7891033518029</t>
+  </si>
+  <si>
+    <t>7891033520237</t>
+  </si>
+  <si>
+    <t>7891033526390</t>
+  </si>
+  <si>
+    <t>7891033527465</t>
+  </si>
+  <si>
+    <t>7891033530946</t>
+  </si>
+  <si>
+    <t>7891033530953</t>
+  </si>
+  <si>
+    <t>7891033531448</t>
+  </si>
+  <si>
+    <t>7891033533558</t>
+  </si>
+  <si>
+    <t>7891033534371</t>
+  </si>
+  <si>
+    <t>7891033534395</t>
+  </si>
+  <si>
+    <t>7891033534401</t>
+  </si>
+  <si>
+    <t>7891033534418</t>
+  </si>
+  <si>
+    <t>7891033535002</t>
+  </si>
+  <si>
+    <t>7891033535019</t>
+  </si>
+  <si>
+    <t>7891033535057</t>
+  </si>
+  <si>
+    <t>7891033539222</t>
+  </si>
+  <si>
+    <t>7891033548873</t>
+  </si>
+  <si>
+    <t>7891033556748</t>
+  </si>
+  <si>
+    <t>7891033556755</t>
+  </si>
+  <si>
+    <t>7891033557639</t>
+  </si>
+  <si>
+    <t>7891033558025</t>
+  </si>
+  <si>
+    <t>7891033558032</t>
+  </si>
+  <si>
+    <t>7891033558049</t>
+  </si>
+  <si>
+    <t>7891033558056</t>
+  </si>
+  <si>
+    <t>7891033559572</t>
+  </si>
+  <si>
+    <t>7891033559589</t>
+  </si>
+  <si>
+    <t>7891033560059</t>
+  </si>
+  <si>
+    <t>7891033564583</t>
+  </si>
+  <si>
+    <t>7891033564590</t>
+  </si>
+  <si>
+    <t>7891033570850</t>
+  </si>
+  <si>
+    <t>7891033580569</t>
+  </si>
+  <si>
+    <t>7891033581191</t>
+  </si>
+  <si>
+    <t>7891033581207</t>
+  </si>
+  <si>
+    <t>7891033581214</t>
+  </si>
+  <si>
+    <t>7891033583072</t>
+  </si>
+  <si>
+    <t>7891033583089</t>
+  </si>
+  <si>
+    <t>7891033586332</t>
+  </si>
+  <si>
+    <t>7891033590124</t>
+  </si>
+  <si>
+    <t>7891033595839</t>
+  </si>
+  <si>
+    <t>7891033706686</t>
+  </si>
+  <si>
+    <t>7891033706938</t>
+  </si>
+  <si>
+    <t>7891033740963</t>
+  </si>
+  <si>
+    <t>7891033779901</t>
+  </si>
+  <si>
+    <t>7891033793761</t>
+  </si>
+  <si>
+    <t>7891033842148</t>
+  </si>
+  <si>
+    <t>7891033843886</t>
+  </si>
+  <si>
+    <t>7891033843909</t>
+  </si>
+  <si>
+    <t>7891033848645</t>
+  </si>
+  <si>
+    <t>7891033848690</t>
+  </si>
+  <si>
+    <t>7891033848744</t>
+  </si>
+  <si>
+    <t>7891033850211</t>
+  </si>
+  <si>
+    <t>7891033853083</t>
+  </si>
+  <si>
+    <t>7891033853953</t>
+  </si>
+  <si>
+    <t>7891033855476</t>
+  </si>
+  <si>
+    <t>7891033856060</t>
+  </si>
+  <si>
+    <t>7891033856442</t>
+  </si>
+  <si>
+    <t>7891033858286</t>
+  </si>
+  <si>
+    <t>7891033858996</t>
+  </si>
+  <si>
+    <t>7891033861675</t>
+  </si>
+  <si>
+    <t>7891033862252</t>
+  </si>
+  <si>
+    <t>7891033862597</t>
+  </si>
+  <si>
+    <t>7891033862603</t>
+  </si>
+  <si>
+    <t>7891033863204</t>
+  </si>
+  <si>
+    <t>7891033864317</t>
+  </si>
+  <si>
+    <t>7891033865338</t>
+  </si>
+  <si>
+    <t>7891033865352</t>
+  </si>
+  <si>
+    <t>7891033867097</t>
+  </si>
+  <si>
+    <t>7891033867561</t>
+  </si>
+  <si>
+    <t>7891033868759</t>
+  </si>
+  <si>
+    <t>7891033868933</t>
+  </si>
+  <si>
+    <t>7891033868957</t>
+  </si>
+  <si>
+    <t>7891033871353</t>
+  </si>
+  <si>
+    <t>7891033871360</t>
+  </si>
+  <si>
+    <t>7891033873289</t>
+  </si>
+  <si>
+    <t>7891033873401</t>
+  </si>
+  <si>
+    <t>7891033874538</t>
+  </si>
+  <si>
+    <t>7891033874835</t>
+  </si>
+  <si>
+    <t>7891033875573</t>
+  </si>
+  <si>
+    <t>7891033876006</t>
+  </si>
+  <si>
+    <t>7891033877799</t>
+  </si>
+  <si>
+    <t>7891033878031</t>
+  </si>
+  <si>
+    <t>7891033879175</t>
+  </si>
+  <si>
+    <t>7891033880072</t>
+  </si>
+  <si>
+    <t>7891033880089</t>
+  </si>
+  <si>
+    <t>7891033880560</t>
+  </si>
+  <si>
+    <t>7891033882038</t>
+  </si>
+  <si>
+    <t>7891033882953</t>
+  </si>
+  <si>
+    <t>7891033885152</t>
+  </si>
+  <si>
+    <t>7891033885183</t>
+  </si>
+  <si>
+    <t>7891033885206</t>
+  </si>
+  <si>
+    <t>7891033885565</t>
+  </si>
+  <si>
+    <t>7891033887026</t>
+  </si>
+  <si>
+    <t>7891033890316</t>
+  </si>
+  <si>
+    <t>7891033892723</t>
+  </si>
+  <si>
+    <t>7891033893317</t>
+  </si>
+  <si>
+    <t>7891033896783</t>
+  </si>
+  <si>
+    <t>7891033896790</t>
+  </si>
+  <si>
+    <t>7891033896806</t>
+  </si>
+  <si>
+    <t>7891033896813</t>
+  </si>
+  <si>
+    <t>7891033897896</t>
+  </si>
+  <si>
+    <t>7891033898169</t>
+  </si>
+  <si>
+    <t>7891033901128</t>
+  </si>
+  <si>
+    <t>7891033906277</t>
+  </si>
+  <si>
+    <t>7891033906314</t>
+  </si>
+  <si>
+    <t>7891033906321</t>
+  </si>
+  <si>
+    <t>7891033906338</t>
+  </si>
+  <si>
+    <t>7891033906635</t>
+  </si>
+  <si>
+    <t>7891033906727</t>
+  </si>
+  <si>
+    <t>7891033906895</t>
+  </si>
+  <si>
+    <t>7891033906970</t>
+  </si>
+  <si>
+    <t>7891033907212</t>
+  </si>
+  <si>
+    <t>7891033907274</t>
+  </si>
+  <si>
+    <t>7891033908936</t>
+  </si>
+  <si>
+    <t>7891033930623</t>
+  </si>
+  <si>
+    <t>7891033935482</t>
+  </si>
+  <si>
+    <t>7891033941964</t>
+  </si>
+  <si>
+    <t>7891033942121</t>
+  </si>
+  <si>
+    <t>7891033942138</t>
+  </si>
+  <si>
+    <t>7891033942206</t>
+  </si>
+  <si>
+    <t>7891033942282</t>
+  </si>
+  <si>
+    <t>7891033944019</t>
+  </si>
+  <si>
+    <t>7891033945054</t>
+  </si>
+  <si>
+    <t>7891033946754</t>
+  </si>
+  <si>
+    <t>7891033947508</t>
+  </si>
+  <si>
+    <t>7891033947898</t>
+  </si>
+  <si>
+    <t>7891033948000</t>
+  </si>
+  <si>
+    <t>7891033948031</t>
+  </si>
+  <si>
+    <t>7891033948123</t>
+  </si>
+  <si>
+    <t>7891033948130</t>
+  </si>
+  <si>
+    <t>7891033948147</t>
+  </si>
+  <si>
+    <t>7891033948154</t>
+  </si>
+  <si>
+    <t>7891033948178</t>
+  </si>
+  <si>
+    <t>7891033948185</t>
+  </si>
+  <si>
+    <t>7891033948673</t>
+  </si>
+  <si>
+    <t>7891033949625</t>
+  </si>
+  <si>
+    <t>7891033958023</t>
+  </si>
+  <si>
+    <t>7891033962020</t>
+  </si>
+  <si>
+    <t>7891033977253</t>
   </si>
 </sst>
 </file>
@@ -423,7 +912,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14B8BA79-486A-4311-9DC6-50AF49FF2C77}">
-  <dimension ref="A1:C85"/>
+  <dimension ref="A1:C164"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
@@ -442,65 +931,65 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>1317</v>
-      </c>
-      <c r="B2" s="1">
-        <v>7891033013173</v>
+        <v>1302</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>47629</v>
-      </c>
-      <c r="B3" s="1">
-        <v>7891033476299</v>
+        <v>1314</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>47908</v>
-      </c>
-      <c r="B4" s="1">
-        <v>7891033479085</v>
+        <v>1317</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>48280</v>
-      </c>
-      <c r="B5" s="1">
-        <v>7891033482801</v>
+        <v>1644</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>48634</v>
-      </c>
-      <c r="B6" s="1">
-        <v>7891033486342</v>
+        <v>19734</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>48653</v>
-      </c>
-      <c r="B7" s="1">
-        <v>7891033486533</v>
+        <v>40220</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -508,21 +997,21 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>48664</v>
-      </c>
-      <c r="B8" s="1">
-        <v>7891033486649</v>
+        <v>46898</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>49154</v>
-      </c>
-      <c r="B9" s="1">
-        <v>7891033491544</v>
+        <v>47629</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -530,197 +1019,197 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>49250</v>
-      </c>
-      <c r="B10" s="1">
-        <v>7891033492503</v>
+        <v>47630</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>49252</v>
-      </c>
-      <c r="B11" s="1">
-        <v>7891033492527</v>
+        <v>47908</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>50012</v>
-      </c>
-      <c r="B12" s="1">
-        <v>7891033500123</v>
+        <v>48280</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="C12">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>50022</v>
-      </c>
-      <c r="B13" s="1">
-        <v>7891033500222</v>
+        <v>48296</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="C13">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>50677</v>
-      </c>
-      <c r="B14" s="1">
-        <v>7891033506774</v>
+        <v>48315</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>50881</v>
-      </c>
-      <c r="B15" s="1">
-        <v>7891033508815</v>
+        <v>48375</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>51745</v>
-      </c>
-      <c r="B16" s="1">
-        <v>7891033517459</v>
+        <v>48664</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>51746</v>
-      </c>
-      <c r="B17" s="1">
-        <v>7891033517466</v>
+        <v>49250</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>52022</v>
-      </c>
-      <c r="B18" s="1">
-        <v>7891033520220</v>
+        <v>49252</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>52589</v>
-      </c>
-      <c r="B19" s="1">
-        <v>7891033525898</v>
+        <v>49765</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>52752</v>
-      </c>
-      <c r="B20" s="1">
-        <v>7891033527526</v>
+        <v>49812</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>53094</v>
-      </c>
-      <c r="B21" s="1">
-        <v>7891033530946</v>
+        <v>50012</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>53159</v>
-      </c>
-      <c r="B22" s="1">
-        <v>7891033531592</v>
+        <v>50014</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>53500</v>
-      </c>
-      <c r="B23" s="1">
-        <v>7891033535002</v>
+        <v>51441</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>53501</v>
-      </c>
-      <c r="B24" s="1">
-        <v>7891033535019</v>
+        <v>51745</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="C24">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>53504</v>
-      </c>
-      <c r="B25" s="1">
-        <v>7891033535040</v>
+        <v>51746</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="C25">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>53922</v>
-      </c>
-      <c r="B26" s="1">
-        <v>7891033539222</v>
+        <v>51749</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="C26">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>54887</v>
-      </c>
-      <c r="B27" s="1">
-        <v>7891033548873</v>
+        <v>51802</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="C27">
         <v>3</v>
@@ -728,65 +1217,65 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>55957</v>
-      </c>
-      <c r="B28" s="1">
-        <v>7891033559572</v>
+        <v>52023</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>55958</v>
-      </c>
-      <c r="B29" s="1">
-        <v>7891033559589</v>
+        <v>52639</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="C29">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>56458</v>
-      </c>
-      <c r="B30" s="1">
-        <v>7891033564583</v>
+        <v>52746</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="C30">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>56459</v>
-      </c>
-      <c r="B31" s="1">
-        <v>7891033564590</v>
+        <v>53094</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="C31">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>56686</v>
-      </c>
-      <c r="B32" s="1">
-        <v>7891033566860</v>
+        <v>53095</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>56796</v>
-      </c>
-      <c r="B33" s="1">
-        <v>7891033567966</v>
+        <v>53144</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="C33">
         <v>2</v>
@@ -794,98 +1283,98 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>58633</v>
-      </c>
-      <c r="B34" s="1">
-        <v>7891033586332</v>
+        <v>53355</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="C34">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>59555</v>
-      </c>
-      <c r="B35" s="1">
-        <v>7891033595556</v>
+        <v>53437</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="C35">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>59845</v>
-      </c>
-      <c r="B36" s="1">
-        <v>7891033598458</v>
+        <v>53439</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="C36">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>74103</v>
-      </c>
-      <c r="B37" s="1">
-        <v>7891033741038</v>
+        <v>53440</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="C37">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>74438</v>
-      </c>
-      <c r="B38" s="1">
-        <v>7891033744381</v>
+        <v>53441</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="C38">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>76621</v>
-      </c>
-      <c r="B39" s="1">
-        <v>7891033766215</v>
+        <v>53500</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="C39">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>76700</v>
-      </c>
-      <c r="B40" s="1">
-        <v>7891033767007</v>
+        <v>53501</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="C40">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>77990</v>
-      </c>
-      <c r="B41" s="1">
-        <v>7891033779901</v>
+        <v>53505</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="C41">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>79998</v>
-      </c>
-      <c r="B42" s="1">
-        <v>7891033799985</v>
+        <v>53922</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -893,87 +1382,87 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>80849</v>
-      </c>
-      <c r="B43" s="1">
-        <v>7891033808496</v>
+        <v>54887</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="C43">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>82052</v>
-      </c>
-      <c r="B44" s="1">
-        <v>7891033820528</v>
+        <v>55674</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="C44">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>82091</v>
-      </c>
-      <c r="B45" s="1">
-        <v>7891033820917</v>
+        <v>55675</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="C45">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>82685</v>
-      </c>
-      <c r="B46" s="1">
-        <v>7891033826858</v>
+        <v>55763</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C46">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>82686</v>
-      </c>
-      <c r="B47" s="1">
-        <v>7891033826865</v>
+        <v>55802</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="C47">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>82688</v>
-      </c>
-      <c r="B48" s="1">
-        <v>7891033826889</v>
+        <v>55803</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="C48">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>82689</v>
-      </c>
-      <c r="B49" s="1">
-        <v>7891033826896</v>
+        <v>55804</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="C49">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>83823</v>
-      </c>
-      <c r="B50" s="1">
-        <v>7891033838233</v>
+        <v>55805</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="C50">
         <v>2</v>
@@ -981,120 +1470,120 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>83971</v>
-      </c>
-      <c r="B51" s="1">
-        <v>7891033839711</v>
+        <v>55957</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="C51">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>84113</v>
-      </c>
-      <c r="B52" s="1">
-        <v>7891033841134</v>
+        <v>55958</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="C52">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>84182</v>
-      </c>
-      <c r="B53" s="1">
-        <v>7891033841820</v>
+        <v>56005</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="C53">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>84213</v>
-      </c>
-      <c r="B54" s="1">
-        <v>7891033842131</v>
+        <v>56458</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="C54">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>84390</v>
-      </c>
-      <c r="B55" s="1">
-        <v>7891033843909</v>
+        <v>56459</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="C55">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>84392</v>
-      </c>
-      <c r="B56" s="1">
-        <v>7891033843923</v>
-      </c>
-      <c r="C56">
-        <v>3</v>
+        <v>57085</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C56" t="e">
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>84399</v>
-      </c>
-      <c r="B57" s="1">
-        <v>7891033843992</v>
+        <v>58056</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="C57">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>85120</v>
-      </c>
-      <c r="B58" s="1">
-        <v>7891033851201</v>
+        <v>58119</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="C58">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>85308</v>
-      </c>
-      <c r="B59" s="1">
-        <v>7891033853083</v>
+        <v>58120</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="C59">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>85543</v>
-      </c>
-      <c r="B60" s="1">
-        <v>7891033855438</v>
+        <v>58121</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="C60">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>85645</v>
-      </c>
-      <c r="B61" s="1">
-        <v>7891033856459</v>
+        <v>58307</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="C61">
         <v>2</v>
@@ -1102,76 +1591,76 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>86225</v>
-      </c>
-      <c r="B62" s="1">
-        <v>7891033862252</v>
+        <v>58308</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="C62">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>86431</v>
-      </c>
-      <c r="B63" s="1">
-        <v>7891033864317</v>
+        <v>58633</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="C63">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>86465</v>
-      </c>
-      <c r="B64" s="1">
-        <v>7891033864652</v>
+        <v>59012</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C64">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>87135</v>
-      </c>
-      <c r="B65" s="1">
-        <v>7891033871353</v>
+        <v>59583</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="C65">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>87136</v>
-      </c>
-      <c r="B66" s="1">
-        <v>7891033871360</v>
+        <v>70668</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="C66">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>87328</v>
-      </c>
-      <c r="B67" s="1">
-        <v>7891033873289</v>
+        <v>70693</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="C67">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>87807</v>
-      </c>
-      <c r="B68" s="1">
-        <v>7891033878079</v>
+        <v>74096</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="C68">
         <v>2</v>
@@ -1179,142 +1668,142 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>87896</v>
-      </c>
-      <c r="B69" s="1">
-        <v>7891033878963</v>
+        <v>77990</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="C69">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>88135</v>
-      </c>
-      <c r="B70" s="1">
-        <v>7891033881352</v>
+        <v>79376</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="C70">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>88203</v>
-      </c>
-      <c r="B71" s="1">
-        <v>7891033882038</v>
+        <v>84214</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="C71">
-        <v>37</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>88209</v>
-      </c>
-      <c r="B72" s="1">
-        <v>7891033882090</v>
+        <v>84388</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="C72">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>89272</v>
-      </c>
-      <c r="B73" s="1">
-        <v>7891033892723</v>
+        <v>84390</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="C73">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>89281</v>
-      </c>
-      <c r="B74" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C74">
-        <v>4</v>
+        <v>84864</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C74" t="e">
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>89331</v>
-      </c>
-      <c r="B75" s="1">
-        <v>7891033893317</v>
-      </c>
-      <c r="C75">
-        <v>4</v>
+        <v>84869</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C75" t="e">
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>89678</v>
-      </c>
-      <c r="B76" s="1">
-        <v>7891033896783</v>
-      </c>
-      <c r="C76">
-        <v>5</v>
+        <v>84874</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C76" t="e">
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>89679</v>
-      </c>
-      <c r="B77" s="1">
-        <v>7891033896790</v>
-      </c>
-      <c r="C77">
-        <v>5</v>
+        <v>85021</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C77" t="e">
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>89680</v>
-      </c>
-      <c r="B78" s="1">
-        <v>7891033896806</v>
+        <v>85308</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="C78">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>89681</v>
-      </c>
-      <c r="B79" s="1">
-        <v>7891033896813</v>
+        <v>85395</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="C79">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>89816</v>
-      </c>
-      <c r="B80" s="1">
-        <v>7891033898169</v>
+        <v>85547</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="C80">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>90310</v>
-      </c>
-      <c r="B81" s="1">
-        <v>7891033903108</v>
+        <v>85606</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>82</v>
       </c>
       <c r="C81">
         <v>3</v>
@@ -1322,46 +1811,915 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>90513</v>
-      </c>
-      <c r="B82" s="1">
-        <v>7891033905133</v>
+        <v>85644</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="C82">
-        <v>37</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>93548</v>
-      </c>
-      <c r="B83" s="1">
-        <v>7891033935482</v>
-      </c>
-      <c r="C83">
-        <v>3</v>
+        <v>85828</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C83" t="e">
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>94758</v>
-      </c>
-      <c r="B84" s="1">
-        <v>7891033947584</v>
+        <v>85899</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>85</v>
       </c>
       <c r="C84">
-        <v>33</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>96399</v>
-      </c>
-      <c r="B85" s="1">
-        <v>7891033963997</v>
+        <v>86167</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="C85">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>86225</v>
+      </c>
+      <c r="B86" t="s">
+        <v>87</v>
+      </c>
+      <c r="C86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>86259</v>
+      </c>
+      <c r="B87" t="s">
+        <v>88</v>
+      </c>
+      <c r="C87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>86260</v>
+      </c>
+      <c r="B88" t="s">
+        <v>89</v>
+      </c>
+      <c r="C88" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>86320</v>
+      </c>
+      <c r="B89" t="s">
+        <v>90</v>
+      </c>
+      <c r="C89" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>86431</v>
+      </c>
+      <c r="B90" t="s">
+        <v>91</v>
+      </c>
+      <c r="C90">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>86533</v>
+      </c>
+      <c r="B91" t="s">
+        <v>92</v>
+      </c>
+      <c r="C91" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>86535</v>
+      </c>
+      <c r="B92" t="s">
+        <v>93</v>
+      </c>
+      <c r="C92" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>86709</v>
+      </c>
+      <c r="B93" t="s">
+        <v>94</v>
+      </c>
+      <c r="C93" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>86756</v>
+      </c>
+      <c r="B94" t="s">
+        <v>95</v>
+      </c>
+      <c r="C94" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>86875</v>
+      </c>
+      <c r="B95" t="s">
+        <v>96</v>
+      </c>
+      <c r="C95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>86893</v>
+      </c>
+      <c r="B96" t="s">
+        <v>97</v>
+      </c>
+      <c r="C96">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>86895</v>
+      </c>
+      <c r="B97" t="s">
+        <v>98</v>
+      </c>
+      <c r="C97">
         <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>87135</v>
+      </c>
+      <c r="B98" t="s">
+        <v>99</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>87136</v>
+      </c>
+      <c r="B99" t="s">
+        <v>100</v>
+      </c>
+      <c r="C99">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>87328</v>
+      </c>
+      <c r="B100" t="s">
+        <v>101</v>
+      </c>
+      <c r="C100">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>87340</v>
+      </c>
+      <c r="B101" t="s">
+        <v>102</v>
+      </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>87453</v>
+      </c>
+      <c r="B102" t="s">
+        <v>103</v>
+      </c>
+      <c r="C102">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>87483</v>
+      </c>
+      <c r="B103" t="s">
+        <v>104</v>
+      </c>
+      <c r="C103" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>87557</v>
+      </c>
+      <c r="B104" t="s">
+        <v>105</v>
+      </c>
+      <c r="C104">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>87600</v>
+      </c>
+      <c r="B105" t="s">
+        <v>106</v>
+      </c>
+      <c r="C105" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>87779</v>
+      </c>
+      <c r="B106" t="s">
+        <v>107</v>
+      </c>
+      <c r="C106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>87803</v>
+      </c>
+      <c r="B107" t="s">
+        <v>108</v>
+      </c>
+      <c r="C107" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>87917</v>
+      </c>
+      <c r="B108" t="s">
+        <v>109</v>
+      </c>
+      <c r="C108" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>88007</v>
+      </c>
+      <c r="B109" t="s">
+        <v>110</v>
+      </c>
+      <c r="C109">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>88008</v>
+      </c>
+      <c r="B110" t="s">
+        <v>111</v>
+      </c>
+      <c r="C110">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>88056</v>
+      </c>
+      <c r="B111" t="s">
+        <v>112</v>
+      </c>
+      <c r="C111" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>88203</v>
+      </c>
+      <c r="B112" t="s">
+        <v>113</v>
+      </c>
+      <c r="C112">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>88295</v>
+      </c>
+      <c r="B113" t="s">
+        <v>114</v>
+      </c>
+      <c r="C113">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>88515</v>
+      </c>
+      <c r="B114" t="s">
+        <v>115</v>
+      </c>
+      <c r="C114" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>88518</v>
+      </c>
+      <c r="B115" t="s">
+        <v>116</v>
+      </c>
+      <c r="C115" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>88520</v>
+      </c>
+      <c r="B116" t="s">
+        <v>117</v>
+      </c>
+      <c r="C116" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>88556</v>
+      </c>
+      <c r="B117" t="s">
+        <v>118</v>
+      </c>
+      <c r="C117" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>88702</v>
+      </c>
+      <c r="B118" t="s">
+        <v>119</v>
+      </c>
+      <c r="C118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>89031</v>
+      </c>
+      <c r="B119" t="s">
+        <v>120</v>
+      </c>
+      <c r="C119" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>89272</v>
+      </c>
+      <c r="B120" t="s">
+        <v>121</v>
+      </c>
+      <c r="C120">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>89331</v>
+      </c>
+      <c r="B121" t="s">
+        <v>122</v>
+      </c>
+      <c r="C121">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>89678</v>
+      </c>
+      <c r="B122" t="s">
+        <v>123</v>
+      </c>
+      <c r="C122">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>89679</v>
+      </c>
+      <c r="B123" t="s">
+        <v>124</v>
+      </c>
+      <c r="C123">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>89680</v>
+      </c>
+      <c r="B124" t="s">
+        <v>125</v>
+      </c>
+      <c r="C124">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>89681</v>
+      </c>
+      <c r="B125" t="s">
+        <v>126</v>
+      </c>
+      <c r="C125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>89789</v>
+      </c>
+      <c r="B126" t="s">
+        <v>127</v>
+      </c>
+      <c r="C126" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>89816</v>
+      </c>
+      <c r="B127" t="s">
+        <v>128</v>
+      </c>
+      <c r="C127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>90112</v>
+      </c>
+      <c r="B128" t="s">
+        <v>129</v>
+      </c>
+      <c r="C128" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>90627</v>
+      </c>
+      <c r="B129" t="s">
+        <v>130</v>
+      </c>
+      <c r="C129" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>90631</v>
+      </c>
+      <c r="B130" t="s">
+        <v>131</v>
+      </c>
+      <c r="C130" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>90632</v>
+      </c>
+      <c r="B131" t="s">
+        <v>132</v>
+      </c>
+      <c r="C131" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>90633</v>
+      </c>
+      <c r="B132" t="s">
+        <v>133</v>
+      </c>
+      <c r="C132" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>90663</v>
+      </c>
+      <c r="B133" t="s">
+        <v>134</v>
+      </c>
+      <c r="C133" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>90672</v>
+      </c>
+      <c r="B134" t="s">
+        <v>135</v>
+      </c>
+      <c r="C134" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>90689</v>
+      </c>
+      <c r="B135" t="s">
+        <v>136</v>
+      </c>
+      <c r="C135" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>90697</v>
+      </c>
+      <c r="B136" t="s">
+        <v>137</v>
+      </c>
+      <c r="C136" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>90721</v>
+      </c>
+      <c r="B137" t="s">
+        <v>138</v>
+      </c>
+      <c r="C137" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>90727</v>
+      </c>
+      <c r="B138" t="s">
+        <v>139</v>
+      </c>
+      <c r="C138" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>90893</v>
+      </c>
+      <c r="B139" t="s">
+        <v>140</v>
+      </c>
+      <c r="C139" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>93062</v>
+      </c>
+      <c r="B140" t="s">
+        <v>141</v>
+      </c>
+      <c r="C140">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>93548</v>
+      </c>
+      <c r="B141" t="s">
+        <v>142</v>
+      </c>
+      <c r="C141">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>94196</v>
+      </c>
+      <c r="B142" t="s">
+        <v>143</v>
+      </c>
+      <c r="C142" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>94212</v>
+      </c>
+      <c r="B143" t="s">
+        <v>144</v>
+      </c>
+      <c r="C143" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>94213</v>
+      </c>
+      <c r="B144" t="s">
+        <v>145</v>
+      </c>
+      <c r="C144" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>94220</v>
+      </c>
+      <c r="B145" t="s">
+        <v>146</v>
+      </c>
+      <c r="C145" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>94228</v>
+      </c>
+      <c r="B146" t="s">
+        <v>147</v>
+      </c>
+      <c r="C146" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>94401</v>
+      </c>
+      <c r="B147" t="s">
+        <v>148</v>
+      </c>
+      <c r="C147">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>94505</v>
+      </c>
+      <c r="B148" t="s">
+        <v>149</v>
+      </c>
+      <c r="C148" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>94675</v>
+      </c>
+      <c r="B149" t="s">
+        <v>150</v>
+      </c>
+      <c r="C149" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>94750</v>
+      </c>
+      <c r="B150" t="s">
+        <v>151</v>
+      </c>
+      <c r="C150">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>94789</v>
+      </c>
+      <c r="B151" t="s">
+        <v>152</v>
+      </c>
+      <c r="C151" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>94800</v>
+      </c>
+      <c r="B152" t="s">
+        <v>153</v>
+      </c>
+      <c r="C152" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>94803</v>
+      </c>
+      <c r="B153" t="s">
+        <v>154</v>
+      </c>
+      <c r="C153" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>94812</v>
+      </c>
+      <c r="B154" t="s">
+        <v>155</v>
+      </c>
+      <c r="C154" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>94813</v>
+      </c>
+      <c r="B155" t="s">
+        <v>156</v>
+      </c>
+      <c r="C155" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>94814</v>
+      </c>
+      <c r="B156" t="s">
+        <v>157</v>
+      </c>
+      <c r="C156" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>94815</v>
+      </c>
+      <c r="B157" t="s">
+        <v>158</v>
+      </c>
+      <c r="C157">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>94817</v>
+      </c>
+      <c r="B158" t="s">
+        <v>159</v>
+      </c>
+      <c r="C158" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>94818</v>
+      </c>
+      <c r="B159" t="s">
+        <v>160</v>
+      </c>
+      <c r="C159" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>94867</v>
+      </c>
+      <c r="B160" t="s">
+        <v>161</v>
+      </c>
+      <c r="C160" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>94962</v>
+      </c>
+      <c r="B161" t="s">
+        <v>162</v>
+      </c>
+      <c r="C161" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>95802</v>
+      </c>
+      <c r="B162" t="s">
+        <v>163</v>
+      </c>
+      <c r="C162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>96202</v>
+      </c>
+      <c r="B163" t="s">
+        <v>164</v>
+      </c>
+      <c r="C163" t="e">
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>97725</v>
+      </c>
+      <c r="B164" t="s">
+        <v>165</v>
+      </c>
+      <c r="C164" t="e">
+        <v>#N/A</v>
       </c>
     </row>
   </sheetData>

--- a/Programa conferencia.xlsx
+++ b/Programa conferencia.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Apoio1\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Apoio1\Desktop\sistema-conferencia-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0CFFA5D-869F-4B86-9C3A-0CCFD9C84C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFF65C10-C1D2-4A13-9321-739804A415ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{D9876C19-AA45-4750-98F6-B6407576DC16}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="174">
   <si>
     <t>Código do Produto</t>
   </si>
@@ -62,31 +62,34 @@
     <t>7891033013173</t>
   </si>
   <si>
-    <t>7891033016440</t>
-  </si>
-  <si>
-    <t>7891033197347</t>
+    <t>7891033016419</t>
+  </si>
+  <si>
+    <t>7891033070664</t>
+  </si>
+  <si>
+    <t>7891033072347</t>
+  </si>
+  <si>
+    <t>7891033129676</t>
   </si>
   <si>
     <t>7891033402205</t>
   </si>
   <si>
-    <t>7891033468980</t>
-  </si>
-  <si>
-    <t>7891033476299</t>
+    <t>7891033471775</t>
   </si>
   <si>
     <t>7891033476305</t>
   </si>
   <si>
-    <t>7891033479085</t>
-  </si>
-  <si>
-    <t>7891033482801</t>
-  </si>
-  <si>
-    <t>7891033482962</t>
+    <t>7891033478873</t>
+  </si>
+  <si>
+    <t>7891033478880</t>
+  </si>
+  <si>
+    <t>7891033481439</t>
   </si>
   <si>
     <t>7891033483150</t>
@@ -95,28 +98,31 @@
     <t>7891033483754</t>
   </si>
   <si>
-    <t>7891033486649</t>
-  </si>
-  <si>
-    <t>7891033492503</t>
-  </si>
-  <si>
-    <t>7891033492527</t>
+    <t>7891033487851</t>
+  </si>
+  <si>
+    <t>7891033495436</t>
+  </si>
+  <si>
+    <t>7891033495795</t>
   </si>
   <si>
     <t>7891033497652</t>
   </si>
   <si>
-    <t>7891033498123</t>
-  </si>
-  <si>
-    <t>7891033500123</t>
-  </si>
-  <si>
     <t>7891033500147</t>
   </si>
   <si>
-    <t>7891033514410</t>
+    <t>7891033502677</t>
+  </si>
+  <si>
+    <t>7891033509317</t>
+  </si>
+  <si>
+    <t>7891033512270</t>
+  </si>
+  <si>
+    <t>7891033512317</t>
   </si>
   <si>
     <t>7891033517459</t>
@@ -128,66 +134,72 @@
     <t>7891033517497</t>
   </si>
   <si>
-    <t>7891033518029</t>
-  </si>
-  <si>
-    <t>7891033520237</t>
-  </si>
-  <si>
-    <t>7891033526390</t>
+    <t>7891033518081</t>
+  </si>
+  <si>
+    <t>7891033520190</t>
+  </si>
+  <si>
+    <t>7891033521685</t>
+  </si>
+  <si>
+    <t>7891033527458</t>
   </si>
   <si>
     <t>7891033527465</t>
   </si>
   <si>
+    <t>7891033527472</t>
+  </si>
+  <si>
+    <t>7891033527489</t>
+  </si>
+  <si>
+    <t>7891033529438</t>
+  </si>
+  <si>
     <t>7891033530946</t>
   </si>
   <si>
     <t>7891033530953</t>
   </si>
   <si>
-    <t>7891033531448</t>
-  </si>
-  <si>
-    <t>7891033533558</t>
-  </si>
-  <si>
-    <t>7891033534371</t>
-  </si>
-  <si>
-    <t>7891033534395</t>
-  </si>
-  <si>
-    <t>7891033534401</t>
-  </si>
-  <si>
-    <t>7891033534418</t>
-  </si>
-  <si>
-    <t>7891033535002</t>
-  </si>
-  <si>
     <t>7891033535019</t>
   </si>
   <si>
+    <t>7891033535026</t>
+  </si>
+  <si>
+    <t>7891033535040</t>
+  </si>
+  <si>
     <t>7891033535057</t>
   </si>
   <si>
-    <t>7891033539222</t>
+    <t>7891033539796</t>
+  </si>
+  <si>
+    <t>7891033543601</t>
   </si>
   <si>
     <t>7891033548873</t>
   </si>
   <si>
+    <t>7891033554447</t>
+  </si>
+  <si>
+    <t>7891033554744</t>
+  </si>
+  <si>
+    <t>7891033556694</t>
+  </si>
+  <si>
     <t>7891033556748</t>
   </si>
   <si>
     <t>7891033556755</t>
   </si>
   <si>
-    <t>7891033557639</t>
-  </si>
-  <si>
     <t>7891033558025</t>
   </si>
   <si>
@@ -206,16 +218,28 @@
     <t>7891033559589</t>
   </si>
   <si>
-    <t>7891033560059</t>
-  </si>
-  <si>
-    <t>7891033564583</t>
-  </si>
-  <si>
-    <t>7891033564590</t>
-  </si>
-  <si>
-    <t>7891033570850</t>
+    <t>7891033559756</t>
+  </si>
+  <si>
+    <t>7891033563852</t>
+  </si>
+  <si>
+    <t>7891033565276</t>
+  </si>
+  <si>
+    <t>7891033566013</t>
+  </si>
+  <si>
+    <t>7891033566860</t>
+  </si>
+  <si>
+    <t>7891033568116</t>
+  </si>
+  <si>
+    <t>7891033570768</t>
+  </si>
+  <si>
+    <t>7891033574919</t>
   </si>
   <si>
     <t>7891033580569</t>
@@ -230,76 +254,91 @@
     <t>7891033581214</t>
   </si>
   <si>
+    <t>7891033581351</t>
+  </si>
+  <si>
+    <t>7891033582273</t>
+  </si>
+  <si>
+    <t>7891033582310</t>
+  </si>
+  <si>
     <t>7891033583072</t>
   </si>
   <si>
     <t>7891033583089</t>
   </si>
   <si>
-    <t>7891033586332</t>
+    <t>7891033586417</t>
+  </si>
+  <si>
+    <t>7891033589333</t>
+  </si>
+  <si>
+    <t>7891033589876</t>
   </si>
   <si>
     <t>7891033590124</t>
   </si>
   <si>
-    <t>7891033595839</t>
-  </si>
-  <si>
-    <t>7891033706686</t>
-  </si>
-  <si>
-    <t>7891033706938</t>
-  </si>
-  <si>
-    <t>7891033740963</t>
-  </si>
-  <si>
-    <t>7891033779901</t>
-  </si>
-  <si>
-    <t>7891033793761</t>
-  </si>
-  <si>
-    <t>7891033842148</t>
-  </si>
-  <si>
-    <t>7891033843886</t>
+    <t>7891033595174</t>
+  </si>
+  <si>
+    <t>7891033595495</t>
+  </si>
+  <si>
+    <t>7891033595648</t>
+  </si>
+  <si>
+    <t>7891033595655</t>
+  </si>
+  <si>
+    <t>7891033598236</t>
+  </si>
+  <si>
+    <t>7891033767564</t>
+  </si>
+  <si>
+    <t>7891033786206</t>
+  </si>
+  <si>
+    <t>7891033831562</t>
   </si>
   <si>
     <t>7891033843909</t>
   </si>
   <si>
-    <t>7891033848645</t>
-  </si>
-  <si>
-    <t>7891033848690</t>
-  </si>
-  <si>
-    <t>7891033848744</t>
-  </si>
-  <si>
-    <t>7891033850211</t>
+    <t>7891033844005</t>
+  </si>
+  <si>
+    <t>7891033849826</t>
+  </si>
+  <si>
+    <t>7891033851201</t>
   </si>
   <si>
     <t>7891033853083</t>
   </si>
   <si>
+    <t>7891033853137</t>
+  </si>
+  <si>
     <t>7891033853953</t>
   </si>
   <si>
     <t>7891033855476</t>
   </si>
   <si>
-    <t>7891033856060</t>
-  </si>
-  <si>
     <t>7891033856442</t>
   </si>
   <si>
-    <t>7891033858286</t>
-  </si>
-  <si>
-    <t>7891033858996</t>
+    <t>7891033856459</t>
+  </si>
+  <si>
+    <t>7891033857975</t>
+  </si>
+  <si>
+    <t>7891033860319</t>
   </si>
   <si>
     <t>7891033861675</t>
@@ -311,25 +350,19 @@
     <t>7891033862597</t>
   </si>
   <si>
-    <t>7891033862603</t>
-  </si>
-  <si>
-    <t>7891033863204</t>
-  </si>
-  <si>
-    <t>7891033864317</t>
-  </si>
-  <si>
-    <t>7891033865338</t>
-  </si>
-  <si>
-    <t>7891033865352</t>
+    <t>7891033864324</t>
+  </si>
+  <si>
+    <t>7891033867066</t>
+  </si>
+  <si>
+    <t>7891033867073</t>
   </si>
   <si>
     <t>7891033867097</t>
   </si>
   <si>
-    <t>7891033867561</t>
+    <t>7891033867493</t>
   </si>
   <si>
     <t>7891033868759</t>
@@ -341,79 +374,79 @@
     <t>7891033868957</t>
   </si>
   <si>
+    <t>7891033869022</t>
+  </si>
+  <si>
+    <t>7891033870134</t>
+  </si>
+  <si>
+    <t>7891033871315</t>
+  </si>
+  <si>
     <t>7891033871353</t>
   </si>
   <si>
     <t>7891033871360</t>
   </si>
   <si>
+    <t>7891033871438</t>
+  </si>
+  <si>
+    <t>7891033871551</t>
+  </si>
+  <si>
+    <t>7891033872596</t>
+  </si>
+  <si>
+    <t>7891033872923</t>
+  </si>
+  <si>
+    <t>7891033872930</t>
+  </si>
+  <si>
+    <t>7891033872992</t>
+  </si>
+  <si>
+    <t>7891033873005</t>
+  </si>
+  <si>
     <t>7891033873289</t>
   </si>
   <si>
-    <t>7891033873401</t>
-  </si>
-  <si>
-    <t>7891033874538</t>
-  </si>
-  <si>
-    <t>7891033874835</t>
+    <t>7891033873388</t>
+  </si>
+  <si>
+    <t>7891033873807</t>
+  </si>
+  <si>
+    <t>7891033875320</t>
   </si>
   <si>
     <t>7891033875573</t>
   </si>
   <si>
-    <t>7891033876006</t>
+    <t>7891033875597</t>
   </si>
   <si>
     <t>7891033877799</t>
   </si>
   <si>
-    <t>7891033878031</t>
-  </si>
-  <si>
-    <t>7891033879175</t>
-  </si>
-  <si>
-    <t>7891033880072</t>
-  </si>
-  <si>
-    <t>7891033880089</t>
-  </si>
-  <si>
-    <t>7891033880560</t>
-  </si>
-  <si>
-    <t>7891033882038</t>
+    <t>7891033878239</t>
+  </si>
+  <si>
+    <t>7891033879502</t>
+  </si>
+  <si>
+    <t>7891033881352</t>
   </si>
   <si>
     <t>7891033882953</t>
   </si>
   <si>
-    <t>7891033885152</t>
-  </si>
-  <si>
-    <t>7891033885183</t>
-  </si>
-  <si>
-    <t>7891033885206</t>
-  </si>
-  <si>
-    <t>7891033885565</t>
-  </si>
-  <si>
-    <t>7891033887026</t>
-  </si>
-  <si>
-    <t>7891033890316</t>
-  </si>
-  <si>
-    <t>7891033892723</t>
-  </si>
-  <si>
-    <t>7891033893317</t>
-  </si>
-  <si>
-    <t>7891033896783</t>
+    <t>7891033886876</t>
+  </si>
+  <si>
+    <t>7891033887507</t>
   </si>
   <si>
     <t>7891033896790</t>
@@ -425,121 +458,112 @@
     <t>7891033896813</t>
   </si>
   <si>
-    <t>7891033897896</t>
+    <t>7891033897056</t>
+  </si>
+  <si>
+    <t>7891033897155</t>
+  </si>
+  <si>
+    <t>7891033897674</t>
   </si>
   <si>
     <t>7891033898169</t>
   </si>
   <si>
-    <t>7891033901128</t>
-  </si>
-  <si>
-    <t>7891033906277</t>
-  </si>
-  <si>
-    <t>7891033906314</t>
-  </si>
-  <si>
-    <t>7891033906321</t>
-  </si>
-  <si>
-    <t>7891033906338</t>
-  </si>
-  <si>
-    <t>7891033906635</t>
-  </si>
-  <si>
-    <t>7891033906727</t>
-  </si>
-  <si>
-    <t>7891033906895</t>
-  </si>
-  <si>
-    <t>7891033906970</t>
-  </si>
-  <si>
-    <t>7891033907212</t>
-  </si>
-  <si>
-    <t>7891033907274</t>
-  </si>
-  <si>
-    <t>7891033908936</t>
+    <t>7891033902200</t>
+  </si>
+  <si>
+    <t>7891033903221</t>
+  </si>
+  <si>
+    <t>7891033906093</t>
+  </si>
+  <si>
+    <t>7891033908004</t>
+  </si>
+  <si>
+    <t>7891033908035</t>
+  </si>
+  <si>
+    <t>7891033908103</t>
+  </si>
+  <si>
+    <t>7891033908134</t>
+  </si>
+  <si>
+    <t>7891033917211</t>
+  </si>
+  <si>
+    <t>7891033922192</t>
+  </si>
+  <si>
+    <t>7891033930470</t>
   </si>
   <si>
     <t>7891033930623</t>
   </si>
   <si>
+    <t>7891033935420</t>
+  </si>
+  <si>
     <t>7891033935482</t>
   </si>
   <si>
-    <t>7891033941964</t>
-  </si>
-  <si>
-    <t>7891033942121</t>
-  </si>
-  <si>
-    <t>7891033942138</t>
-  </si>
-  <si>
-    <t>7891033942206</t>
-  </si>
-  <si>
-    <t>7891033942282</t>
-  </si>
-  <si>
-    <t>7891033944019</t>
-  </si>
-  <si>
-    <t>7891033945054</t>
-  </si>
-  <si>
-    <t>7891033946754</t>
-  </si>
-  <si>
-    <t>7891033947508</t>
-  </si>
-  <si>
-    <t>7891033947898</t>
-  </si>
-  <si>
-    <t>7891033948000</t>
-  </si>
-  <si>
-    <t>7891033948031</t>
-  </si>
-  <si>
-    <t>7891033948123</t>
-  </si>
-  <si>
-    <t>7891033948130</t>
-  </si>
-  <si>
-    <t>7891033948147</t>
-  </si>
-  <si>
-    <t>7891033948154</t>
-  </si>
-  <si>
-    <t>7891033948178</t>
-  </si>
-  <si>
-    <t>7891033948185</t>
-  </si>
-  <si>
-    <t>7891033948673</t>
-  </si>
-  <si>
-    <t>7891033949625</t>
-  </si>
-  <si>
-    <t>7891033958023</t>
-  </si>
-  <si>
-    <t>7891033962020</t>
-  </si>
-  <si>
-    <t>7891033977253</t>
+    <t>7891033944897</t>
+  </si>
+  <si>
+    <t>7891033944996</t>
+  </si>
+  <si>
+    <t>7891033948208</t>
+  </si>
+  <si>
+    <t>7891033948215</t>
+  </si>
+  <si>
+    <t>7891033948512</t>
+  </si>
+  <si>
+    <t>7891033948529</t>
+  </si>
+  <si>
+    <t>7891033948543</t>
+  </si>
+  <si>
+    <t>7891033948567</t>
+  </si>
+  <si>
+    <t>7891033949847</t>
+  </si>
+  <si>
+    <t>7891033950362</t>
+  </si>
+  <si>
+    <t>7891033950935</t>
+  </si>
+  <si>
+    <t>7891033950942</t>
+  </si>
+  <si>
+    <t>7891033953837</t>
+  </si>
+  <si>
+    <t>7891033954964</t>
+  </si>
+  <si>
+    <t>7891033955329</t>
+  </si>
+  <si>
+    <t>7891033961665</t>
+  </si>
+  <si>
+    <t>7891033966172</t>
+  </si>
+  <si>
+    <t>7891033966264</t>
+  </si>
+  <si>
+    <t>7891033973729</t>
   </si>
 </sst>
 </file>
@@ -912,7 +936,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14B8BA79-486A-4311-9DC6-50AF49FF2C77}">
-  <dimension ref="A1:C164"/>
+  <dimension ref="A1:C172"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
@@ -937,7 +961,7 @@
         <v>3</v>
       </c>
       <c r="C2">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -948,7 +972,7 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -964,29 +988,29 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>1644</v>
+        <v>1641</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>19734</v>
+        <v>7066</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>40220</v>
+        <v>7234</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>8</v>
@@ -997,18 +1021,18 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>46898</v>
+        <v>12967</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>47629</v>
+        <v>40220</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>10</v>
@@ -1019,51 +1043,51 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>47630</v>
+        <v>47177</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>47908</v>
+        <v>47630</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C11">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>48280</v>
+        <v>47887</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>48296</v>
+        <v>47888</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>14</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>48315</v>
+        <v>48143</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>15</v>
@@ -1074,161 +1098,161 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>48375</v>
+        <v>48315</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>48664</v>
+        <v>48375</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>49250</v>
+        <v>48785</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C17">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>49252</v>
+        <v>49543</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C18">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>49765</v>
+        <v>49579</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C19">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>49812</v>
+        <v>49765</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>21</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>50012</v>
+        <v>50014</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C21">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>50014</v>
+        <v>50267</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>23</v>
       </c>
       <c r="C22">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>51441</v>
+        <v>50931</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>51745</v>
+        <v>51227</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>51746</v>
+        <v>51231</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C25">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>51749</v>
+        <v>51745</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>51802</v>
+        <v>51746</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C27">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>52023</v>
+        <v>51749</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>52639</v>
+        <v>51808</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>30</v>
@@ -1239,40 +1263,40 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>52746</v>
+        <v>52019</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>31</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>53094</v>
+        <v>52168</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>53095</v>
+        <v>52745</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>53144</v>
+        <v>52746</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>34</v>
@@ -1283,7 +1307,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>53355</v>
+        <v>52747</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>35</v>
@@ -1294,95 +1318,95 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>53437</v>
+        <v>52748</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>53439</v>
+        <v>52943</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>37</v>
       </c>
       <c r="C36">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>53440</v>
+        <v>53094</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C37">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>53441</v>
+        <v>53095</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C38">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>53500</v>
+        <v>53501</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C39">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>53501</v>
+        <v>53502</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C40">
-        <v>4</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>53505</v>
+        <v>53504</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C41">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>53922</v>
+        <v>53505</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C42">
-        <v>2</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>54887</v>
+        <v>53979</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>44</v>
@@ -1393,183 +1417,183 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>55674</v>
+        <v>54360</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>55675</v>
+        <v>54887</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>55763</v>
+        <v>55444</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>55802</v>
+        <v>55474</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C47">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>55803</v>
+        <v>55669</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C48">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>55804</v>
+        <v>55674</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>55805</v>
+        <v>55675</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C50">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>55957</v>
+        <v>55802</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>55958</v>
+        <v>55803</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C52">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>56005</v>
+        <v>55804</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>54</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>56458</v>
+        <v>55805</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>55</v>
       </c>
       <c r="C54">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>56459</v>
+        <v>55957</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>56</v>
       </c>
       <c r="C55">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>57085</v>
+        <v>55958</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C56" t="e">
-        <v>#DIV/0!</v>
+      <c r="C56">
+        <v>4</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>58056</v>
+        <v>55975</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>58</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>58119</v>
+        <v>56385</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>59</v>
       </c>
       <c r="C58">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>58120</v>
+        <v>56527</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>60</v>
       </c>
       <c r="C59">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>58121</v>
+        <v>56601</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>61</v>
@@ -1580,7 +1604,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>58307</v>
+        <v>56686</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>62</v>
@@ -1591,73 +1615,73 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>58308</v>
+        <v>56811</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>63</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>58633</v>
+        <v>57076</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>64</v>
       </c>
       <c r="C63">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>59012</v>
+        <v>57491</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>65</v>
       </c>
       <c r="C64">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>59583</v>
+        <v>58056</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>66</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>70668</v>
+        <v>58119</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>67</v>
       </c>
       <c r="C66">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>70693</v>
+        <v>58120</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>68</v>
       </c>
       <c r="C67">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>74096</v>
+        <v>58121</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>69</v>
@@ -1668,29 +1692,29 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>77990</v>
+        <v>58135</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>70</v>
       </c>
       <c r="C69">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>79376</v>
+        <v>58227</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>71</v>
       </c>
       <c r="C70">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>84214</v>
+        <v>58231</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>72</v>
@@ -1701,205 +1725,205 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>84388</v>
+        <v>58307</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>73</v>
       </c>
       <c r="C72">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>84390</v>
+        <v>58308</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>74</v>
       </c>
       <c r="C73">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>84864</v>
+        <v>58641</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C74" t="e">
-        <v>#DIV/0!</v>
+      <c r="C74">
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>84869</v>
+        <v>58933</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C75" t="e">
-        <v>#DIV/0!</v>
+      <c r="C75">
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>84874</v>
+        <v>58987</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C76" t="e">
-        <v>#DIV/0!</v>
+      <c r="C76">
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>85021</v>
+        <v>59012</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C77" t="e">
-        <v>#DIV/0!</v>
+      <c r="C77">
+        <v>4</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>85308</v>
+        <v>59517</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>79</v>
       </c>
       <c r="C78">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>85395</v>
+        <v>59549</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>80</v>
       </c>
       <c r="C79">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>85547</v>
+        <v>59564</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>81</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>85606</v>
+        <v>59565</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>82</v>
       </c>
       <c r="C81">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>85644</v>
+        <v>59823</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>83</v>
       </c>
       <c r="C82">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>85828</v>
+        <v>76756</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="C83" t="e">
-        <v>#DIV/0!</v>
+      <c r="C83">
+        <v>2</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>85899</v>
+        <v>78620</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>85</v>
       </c>
       <c r="C84">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>86167</v>
+        <v>83156</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>86</v>
       </c>
       <c r="C85">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>86225</v>
+        <v>84390</v>
       </c>
       <c r="B86" t="s">
         <v>87</v>
       </c>
       <c r="C86">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>86259</v>
+        <v>84400</v>
       </c>
       <c r="B87" t="s">
         <v>88</v>
       </c>
       <c r="C87">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>86260</v>
+        <v>84982</v>
       </c>
       <c r="B88" t="s">
         <v>89</v>
       </c>
-      <c r="C88" t="e">
-        <v>#DIV/0!</v>
+      <c r="C88">
+        <v>7</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>86320</v>
+        <v>85120</v>
       </c>
       <c r="B89" t="s">
         <v>90</v>
       </c>
-      <c r="C89" t="e">
-        <v>#DIV/0!</v>
+      <c r="C89">
+        <v>3</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>86431</v>
+        <v>85308</v>
       </c>
       <c r="B90" t="s">
         <v>91</v>
@@ -1910,73 +1934,73 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>86533</v>
+        <v>85313</v>
       </c>
       <c r="B91" t="s">
         <v>92</v>
       </c>
-      <c r="C91" t="e">
-        <v>#DIV/0!</v>
+      <c r="C91">
+        <v>2</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>86535</v>
+        <v>85395</v>
       </c>
       <c r="B92" t="s">
         <v>93</v>
       </c>
-      <c r="C92" t="e">
-        <v>#DIV/0!</v>
+      <c r="C92">
+        <v>4</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>86709</v>
+        <v>85547</v>
       </c>
       <c r="B93" t="s">
         <v>94</v>
       </c>
-      <c r="C93" t="e">
-        <v>#DIV/0!</v>
+      <c r="C93">
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>86756</v>
+        <v>85644</v>
       </c>
       <c r="B94" t="s">
         <v>95</v>
       </c>
-      <c r="C94" t="e">
-        <v>#DIV/0!</v>
+      <c r="C94">
+        <v>4</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>86875</v>
+        <v>85645</v>
       </c>
       <c r="B95" t="s">
         <v>96</v>
       </c>
       <c r="C95">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>86893</v>
+        <v>85797</v>
       </c>
       <c r="B96" t="s">
         <v>97</v>
       </c>
       <c r="C96">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>86895</v>
+        <v>86031</v>
       </c>
       <c r="B97" t="s">
         <v>98</v>
@@ -1987,249 +2011,249 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>87135</v>
+        <v>86167</v>
       </c>
       <c r="B98" t="s">
         <v>99</v>
       </c>
       <c r="C98">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>87136</v>
+        <v>86225</v>
       </c>
       <c r="B99" t="s">
         <v>100</v>
       </c>
       <c r="C99">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>87328</v>
+        <v>86259</v>
       </c>
       <c r="B100" t="s">
         <v>101</v>
       </c>
       <c r="C100">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>87340</v>
+        <v>86432</v>
       </c>
       <c r="B101" t="s">
         <v>102</v>
       </c>
       <c r="C101">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>87453</v>
+        <v>86706</v>
       </c>
       <c r="B102" t="s">
         <v>103</v>
       </c>
       <c r="C102">
-        <v>3</v>
+        <v>260</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>87483</v>
+        <v>86707</v>
       </c>
       <c r="B103" t="s">
         <v>104</v>
       </c>
-      <c r="C103" t="e">
-        <v>#DIV/0!</v>
+      <c r="C103">
+        <v>22</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>87557</v>
+        <v>86709</v>
       </c>
       <c r="B104" t="s">
         <v>105</v>
       </c>
       <c r="C104">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>87600</v>
+        <v>86749</v>
       </c>
       <c r="B105" t="s">
         <v>106</v>
       </c>
-      <c r="C105" t="e">
-        <v>#DIV/0!</v>
+      <c r="C105">
+        <v>4</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>87779</v>
+        <v>86875</v>
       </c>
       <c r="B106" t="s">
         <v>107</v>
       </c>
       <c r="C106">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>87803</v>
+        <v>86893</v>
       </c>
       <c r="B107" t="s">
         <v>108</v>
       </c>
-      <c r="C107" t="e">
-        <v>#DIV/0!</v>
+      <c r="C107">
+        <v>6</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>87917</v>
+        <v>86895</v>
       </c>
       <c r="B108" t="s">
         <v>109</v>
       </c>
-      <c r="C108" t="e">
-        <v>#DIV/0!</v>
+      <c r="C108">
+        <v>4</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>88007</v>
+        <v>86902</v>
       </c>
       <c r="B109" t="s">
         <v>110</v>
       </c>
       <c r="C109">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>88008</v>
+        <v>87013</v>
       </c>
       <c r="B110" t="s">
         <v>111</v>
       </c>
       <c r="C110">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>88056</v>
+        <v>87131</v>
       </c>
       <c r="B111" t="s">
         <v>112</v>
       </c>
-      <c r="C111" t="e">
-        <v>#DIV/0!</v>
+      <c r="C111">
+        <v>8</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>88203</v>
+        <v>87135</v>
       </c>
       <c r="B112" t="s">
         <v>113</v>
       </c>
       <c r="C112">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>88295</v>
+        <v>87136</v>
       </c>
       <c r="B113" t="s">
         <v>114</v>
       </c>
       <c r="C113">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>88515</v>
+        <v>87143</v>
       </c>
       <c r="B114" t="s">
         <v>115</v>
       </c>
-      <c r="C114" t="e">
-        <v>#DIV/0!</v>
+      <c r="C114">
+        <v>4</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>88518</v>
+        <v>87155</v>
       </c>
       <c r="B115" t="s">
         <v>116</v>
       </c>
-      <c r="C115" t="e">
-        <v>#DIV/0!</v>
+      <c r="C115">
+        <v>2</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>88520</v>
+        <v>87259</v>
       </c>
       <c r="B116" t="s">
         <v>117</v>
       </c>
-      <c r="C116" t="e">
-        <v>#DIV/0!</v>
+      <c r="C116">
+        <v>2</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>88556</v>
+        <v>87292</v>
       </c>
       <c r="B117" t="s">
         <v>118</v>
       </c>
-      <c r="C117" t="e">
-        <v>#DIV/0!</v>
+      <c r="C117">
+        <v>2</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>88702</v>
+        <v>87293</v>
       </c>
       <c r="B118" t="s">
         <v>119</v>
       </c>
       <c r="C118">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>89031</v>
+        <v>87299</v>
       </c>
       <c r="B119" t="s">
         <v>120</v>
       </c>
-      <c r="C119" t="e">
-        <v>#DIV/0!</v>
+      <c r="C119">
+        <v>4</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>89272</v>
+        <v>87300</v>
       </c>
       <c r="B120" t="s">
         <v>121</v>
@@ -2240,403 +2264,403 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>89331</v>
+        <v>87328</v>
       </c>
       <c r="B121" t="s">
         <v>122</v>
       </c>
       <c r="C121">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>89678</v>
+        <v>87338</v>
       </c>
       <c r="B122" t="s">
         <v>123</v>
       </c>
       <c r="C122">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>89679</v>
+        <v>87380</v>
       </c>
       <c r="B123" t="s">
         <v>124</v>
       </c>
       <c r="C123">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>89680</v>
+        <v>87532</v>
       </c>
       <c r="B124" t="s">
         <v>125</v>
       </c>
       <c r="C124">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>89681</v>
+        <v>87557</v>
       </c>
       <c r="B125" t="s">
         <v>126</v>
       </c>
       <c r="C125">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>89789</v>
+        <v>87559</v>
       </c>
       <c r="B126" t="s">
         <v>127</v>
       </c>
-      <c r="C126" t="e">
-        <v>#DIV/0!</v>
+      <c r="C126">
+        <v>2</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>89816</v>
+        <v>87779</v>
       </c>
       <c r="B127" t="s">
         <v>128</v>
       </c>
       <c r="C127">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>90112</v>
+        <v>87823</v>
       </c>
       <c r="B128" t="s">
         <v>129</v>
       </c>
-      <c r="C128" t="e">
-        <v>#DIV/0!</v>
+      <c r="C128">
+        <v>34</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>90627</v>
+        <v>87950</v>
       </c>
       <c r="B129" t="s">
         <v>130</v>
       </c>
-      <c r="C129" t="e">
-        <v>#DIV/0!</v>
+      <c r="C129">
+        <v>2</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>90631</v>
+        <v>88135</v>
       </c>
       <c r="B130" t="s">
         <v>131</v>
       </c>
-      <c r="C130" t="e">
-        <v>#DIV/0!</v>
+      <c r="C130">
+        <v>2</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>90632</v>
+        <v>88295</v>
       </c>
       <c r="B131" t="s">
         <v>132</v>
       </c>
-      <c r="C131" t="e">
-        <v>#DIV/0!</v>
+      <c r="C131">
+        <v>8</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>90633</v>
+        <v>88687</v>
       </c>
       <c r="B132" t="s">
         <v>133</v>
       </c>
-      <c r="C132" t="e">
-        <v>#DIV/0!</v>
+      <c r="C132">
+        <v>2</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>90663</v>
+        <v>88750</v>
       </c>
       <c r="B133" t="s">
         <v>134</v>
       </c>
-      <c r="C133" t="e">
-        <v>#DIV/0!</v>
+      <c r="C133">
+        <v>14</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>90672</v>
+        <v>89679</v>
       </c>
       <c r="B134" t="s">
         <v>135</v>
       </c>
-      <c r="C134" t="e">
-        <v>#DIV/0!</v>
+      <c r="C134">
+        <v>4</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>90689</v>
+        <v>89680</v>
       </c>
       <c r="B135" t="s">
         <v>136</v>
       </c>
-      <c r="C135" t="e">
-        <v>#DIV/0!</v>
+      <c r="C135">
+        <v>44</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>90697</v>
+        <v>89681</v>
       </c>
       <c r="B136" t="s">
         <v>137</v>
       </c>
-      <c r="C136" t="e">
-        <v>#DIV/0!</v>
+      <c r="C136">
+        <v>4</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>90721</v>
+        <v>89705</v>
       </c>
       <c r="B137" t="s">
         <v>138</v>
       </c>
-      <c r="C137" t="e">
-        <v>#DIV/0!</v>
+      <c r="C137">
+        <v>22</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>90727</v>
+        <v>89715</v>
       </c>
       <c r="B138" t="s">
         <v>139</v>
       </c>
-      <c r="C138" t="e">
-        <v>#DIV/0!</v>
+      <c r="C138">
+        <v>6</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>90893</v>
+        <v>89767</v>
       </c>
       <c r="B139" t="s">
         <v>140</v>
       </c>
-      <c r="C139" t="e">
-        <v>#DIV/0!</v>
+      <c r="C139">
+        <v>4</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>93062</v>
+        <v>89816</v>
       </c>
       <c r="B140" t="s">
         <v>141</v>
       </c>
       <c r="C140">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>93548</v>
+        <v>90220</v>
       </c>
       <c r="B141" t="s">
         <v>142</v>
       </c>
       <c r="C141">
-        <v>5</v>
+        <v>120</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>94196</v>
+        <v>90322</v>
       </c>
       <c r="B142" t="s">
         <v>143</v>
       </c>
-      <c r="C142" t="e">
-        <v>#N/A</v>
+      <c r="C142">
+        <v>2</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>94212</v>
+        <v>90609</v>
       </c>
       <c r="B143" t="s">
         <v>144</v>
       </c>
-      <c r="C143" t="e">
-        <v>#DIV/0!</v>
+      <c r="C143">
+        <v>2</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>94213</v>
+        <v>90800</v>
       </c>
       <c r="B144" t="s">
         <v>145</v>
       </c>
-      <c r="C144" t="e">
-        <v>#DIV/0!</v>
+      <c r="C144">
+        <v>60</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>94220</v>
+        <v>90803</v>
       </c>
       <c r="B145" t="s">
         <v>146</v>
       </c>
-      <c r="C145" t="e">
-        <v>#DIV/0!</v>
+      <c r="C145">
+        <v>20</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>94228</v>
+        <v>90810</v>
       </c>
       <c r="B146" t="s">
         <v>147</v>
       </c>
-      <c r="C146" t="e">
-        <v>#DIV/0!</v>
+      <c r="C146">
+        <v>4</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>94401</v>
+        <v>90813</v>
       </c>
       <c r="B147" t="s">
         <v>148</v>
       </c>
       <c r="C147">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>94505</v>
+        <v>91721</v>
       </c>
       <c r="B148" t="s">
         <v>149</v>
       </c>
-      <c r="C148" t="e">
-        <v>#DIV/0!</v>
+      <c r="C148">
+        <v>2</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>94675</v>
+        <v>92219</v>
       </c>
       <c r="B149" t="s">
         <v>150</v>
       </c>
-      <c r="C149" t="e">
-        <v>#DIV/0!</v>
+      <c r="C149">
+        <v>2</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>94750</v>
+        <v>93047</v>
       </c>
       <c r="B150" t="s">
         <v>151</v>
       </c>
       <c r="C150">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>94789</v>
+        <v>93062</v>
       </c>
       <c r="B151" t="s">
         <v>152</v>
       </c>
-      <c r="C151" t="e">
-        <v>#DIV/0!</v>
+      <c r="C151">
+        <v>2</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>94800</v>
+        <v>93542</v>
       </c>
       <c r="B152" t="s">
         <v>153</v>
       </c>
-      <c r="C152" t="e">
-        <v>#DIV/0!</v>
+      <c r="C152">
+        <v>2</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>94803</v>
+        <v>93548</v>
       </c>
       <c r="B153" t="s">
         <v>154</v>
       </c>
-      <c r="C153" t="e">
-        <v>#DIV/0!</v>
+      <c r="C153">
+        <v>10</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>94812</v>
+        <v>94489</v>
       </c>
       <c r="B154" t="s">
         <v>155</v>
       </c>
-      <c r="C154" t="e">
-        <v>#DIV/0!</v>
+      <c r="C154">
+        <v>160</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>94813</v>
+        <v>94499</v>
       </c>
       <c r="B155" t="s">
         <v>156</v>
       </c>
-      <c r="C155" t="e">
-        <v>#DIV/0!</v>
+      <c r="C155">
+        <v>2</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>94814</v>
+        <v>94820</v>
       </c>
       <c r="B156" t="s">
         <v>157</v>
       </c>
-      <c r="C156" t="e">
-        <v>#DIV/0!</v>
+      <c r="C156">
+        <v>4</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>94815</v>
+        <v>94821</v>
       </c>
       <c r="B157" t="s">
         <v>158</v>
@@ -2647,79 +2671,167 @@
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>94817</v>
+        <v>94851</v>
       </c>
       <c r="B158" t="s">
         <v>159</v>
       </c>
-      <c r="C158" t="e">
-        <v>#DIV/0!</v>
+      <c r="C158">
+        <v>182</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>94818</v>
+        <v>94852</v>
       </c>
       <c r="B159" t="s">
         <v>160</v>
       </c>
-      <c r="C159" t="e">
-        <v>#DIV/0!</v>
+      <c r="C159">
+        <v>24</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>94867</v>
+        <v>94854</v>
       </c>
       <c r="B160" t="s">
         <v>161</v>
       </c>
-      <c r="C160" t="e">
-        <v>#DIV/0!</v>
+      <c r="C160">
+        <v>30</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>94962</v>
+        <v>94856</v>
       </c>
       <c r="B161" t="s">
         <v>162</v>
       </c>
-      <c r="C161" t="e">
-        <v>#DIV/0!</v>
+      <c r="C161">
+        <v>14</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>95802</v>
+        <v>94984</v>
       </c>
       <c r="B162" t="s">
         <v>163</v>
       </c>
       <c r="C162">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>96202</v>
+        <v>95036</v>
       </c>
       <c r="B163" t="s">
         <v>164</v>
       </c>
-      <c r="C163" t="e">
-        <v>#DIV/0!</v>
+      <c r="C163">
+        <v>16</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>97725</v>
+        <v>95093</v>
       </c>
       <c r="B164" t="s">
         <v>165</v>
       </c>
-      <c r="C164" t="e">
-        <v>#N/A</v>
+      <c r="C164">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>95094</v>
+      </c>
+      <c r="B165" t="s">
+        <v>166</v>
+      </c>
+      <c r="C165">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>95383</v>
+      </c>
+      <c r="B166" t="s">
+        <v>167</v>
+      </c>
+      <c r="C166">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>95496</v>
+      </c>
+      <c r="B167" t="s">
+        <v>168</v>
+      </c>
+      <c r="C167">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>95532</v>
+      </c>
+      <c r="B168" t="s">
+        <v>169</v>
+      </c>
+      <c r="C168">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>96166</v>
+      </c>
+      <c r="B169" t="s">
+        <v>170</v>
+      </c>
+      <c r="C169">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>96617</v>
+      </c>
+      <c r="B170" t="s">
+        <v>171</v>
+      </c>
+      <c r="C170">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>96626</v>
+      </c>
+      <c r="B171" t="s">
+        <v>172</v>
+      </c>
+      <c r="C171">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>97372</v>
+      </c>
+      <c r="B172" t="s">
+        <v>173</v>
+      </c>
+      <c r="C172">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/Programa conferencia.xlsx
+++ b/Programa conferencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Apoio1\Desktop\sistema-conferencia-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ECFC0B2-C43A-49C5-978F-BFA01CB28F0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D2B14D-02E4-47AA-9840-DFA2AB22F040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{D9876C19-AA45-4750-98F6-B6407576DC16}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
   <si>
     <t>Código do Produto</t>
   </si>
@@ -51,6 +51,231 @@
   </si>
   <si>
     <t>Volumes</t>
+  </si>
+  <si>
+    <t>7891033016440</t>
+  </si>
+  <si>
+    <t>7891033129676</t>
+  </si>
+  <si>
+    <t>7891033471775</t>
+  </si>
+  <si>
+    <t>7891033474011</t>
+  </si>
+  <si>
+    <t>7891033498123</t>
+  </si>
+  <si>
+    <t>7891033512256</t>
+  </si>
+  <si>
+    <t>7891033512270</t>
+  </si>
+  <si>
+    <t>7891033518081</t>
+  </si>
+  <si>
+    <t>7891033520190</t>
+  </si>
+  <si>
+    <t>7891033520527</t>
+  </si>
+  <si>
+    <t>7891033521470</t>
+  </si>
+  <si>
+    <t>7891033534302</t>
+  </si>
+  <si>
+    <t>7891033535002</t>
+  </si>
+  <si>
+    <t>7891033535019</t>
+  </si>
+  <si>
+    <t>7891033535026</t>
+  </si>
+  <si>
+    <t>7891033535040</t>
+  </si>
+  <si>
+    <t>7891033535064</t>
+  </si>
+  <si>
+    <t>7891033535194</t>
+  </si>
+  <si>
+    <t>7891033535200</t>
+  </si>
+  <si>
+    <t>7891033548873</t>
+  </si>
+  <si>
+    <t>7891033556694</t>
+  </si>
+  <si>
+    <t>7891033558025</t>
+  </si>
+  <si>
+    <t>7891033558032</t>
+  </si>
+  <si>
+    <t>7891033581191</t>
+  </si>
+  <si>
+    <t>7891033581207</t>
+  </si>
+  <si>
+    <t>7891033581214</t>
+  </si>
+  <si>
+    <t>7891033583638</t>
+  </si>
+  <si>
+    <t>7891033588459</t>
+  </si>
+  <si>
+    <t>7891033591329</t>
+  </si>
+  <si>
+    <t>7891033598236</t>
+  </si>
+  <si>
+    <t>7891033836840</t>
+  </si>
+  <si>
+    <t>7891033841820</t>
+  </si>
+  <si>
+    <t>7891033842131</t>
+  </si>
+  <si>
+    <t>7891033855476</t>
+  </si>
+  <si>
+    <t>7891033862252</t>
+  </si>
+  <si>
+    <t>7891033869022</t>
+  </si>
+  <si>
+    <t>7891033871087</t>
+  </si>
+  <si>
+    <t>7891033871353</t>
+  </si>
+  <si>
+    <t>7891033873289</t>
+  </si>
+  <si>
+    <t>7891033881352</t>
+  </si>
+  <si>
+    <t>7891033896790</t>
+  </si>
+  <si>
+    <t>7891033897674</t>
+  </si>
+  <si>
+    <t>7891033898169</t>
+  </si>
+  <si>
+    <t>7891033904990</t>
+  </si>
+  <si>
+    <t>7891033905010</t>
+  </si>
+  <si>
+    <t>7891033908134</t>
+  </si>
+  <si>
+    <t>7891033935420</t>
+  </si>
+  <si>
+    <t>7891033941339</t>
+  </si>
+  <si>
+    <t>7891033941346</t>
+  </si>
+  <si>
+    <t>7891033941353</t>
+  </si>
+  <si>
+    <t>7891033941384</t>
+  </si>
+  <si>
+    <t>7891033941391</t>
+  </si>
+  <si>
+    <t>7891033941407</t>
+  </si>
+  <si>
+    <t>7891033941414</t>
+  </si>
+  <si>
+    <t>7891033941421</t>
+  </si>
+  <si>
+    <t>7891033941452</t>
+  </si>
+  <si>
+    <t>7891033941476</t>
+  </si>
+  <si>
+    <t>7891033941483</t>
+  </si>
+  <si>
+    <t>7891033941490</t>
+  </si>
+  <si>
+    <t>7891033941506</t>
+  </si>
+  <si>
+    <t>7891033941544</t>
+  </si>
+  <si>
+    <t>7891033941551</t>
+  </si>
+  <si>
+    <t>7891033941568</t>
+  </si>
+  <si>
+    <t>7891033941582</t>
+  </si>
+  <si>
+    <t>7891033941599</t>
+  </si>
+  <si>
+    <t>7891033941605</t>
+  </si>
+  <si>
+    <t>7891033943050</t>
+  </si>
+  <si>
+    <t>7891033943494</t>
+  </si>
+  <si>
+    <t>7891033944019</t>
+  </si>
+  <si>
+    <t>7891033944996</t>
+  </si>
+  <si>
+    <t>7891033945252</t>
+  </si>
+  <si>
+    <t>7891033945726</t>
+  </si>
+  <si>
+    <t>7891033945740</t>
+  </si>
+  <si>
+    <t>7891033945764</t>
+  </si>
+  <si>
+    <t>7891033946501</t>
   </si>
 </sst>
 </file>
@@ -423,7 +648,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14B8BA79-486A-4311-9DC6-50AF49FF2C77}">
-  <dimension ref="A1:C102"/>
+  <dimension ref="A1:C85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
@@ -442,54 +667,54 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>1302</v>
-      </c>
-      <c r="B2" s="1">
-        <v>7891033013029</v>
+        <v>1644</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="C2">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>1314</v>
-      </c>
-      <c r="B3" s="1">
-        <v>7891033013142</v>
+        <v>12967</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>1317</v>
-      </c>
-      <c r="B4" s="1">
-        <v>7891033013173</v>
+        <v>47177</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>1641</v>
-      </c>
-      <c r="B5" s="1">
-        <v>7891033016419</v>
+        <v>47401</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>1644</v>
-      </c>
-      <c r="B6" s="1">
-        <v>7891033016440</v>
+        <v>49812</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -497,21 +722,21 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>47177</v>
-      </c>
-      <c r="B7" s="1">
-        <v>7891033471775</v>
+        <v>51225</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>47553</v>
-      </c>
-      <c r="B8" s="1">
-        <v>7891033475537</v>
+        <v>51227</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="C8">
         <v>2</v>
@@ -519,21 +744,21 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>47629</v>
-      </c>
-      <c r="B9" s="1">
-        <v>7891033476299</v>
+        <v>51808</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="C9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>47630</v>
-      </c>
-      <c r="B10" s="1">
-        <v>7891033476305</v>
+        <v>52019</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>11</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -541,164 +766,164 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>47908</v>
-      </c>
-      <c r="B11" s="1">
-        <v>7891033479085</v>
+        <v>52052</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="C11">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>49193</v>
-      </c>
-      <c r="B12" s="1">
-        <v>7891033491933</v>
+        <v>52147</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="C12">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>49250</v>
-      </c>
-      <c r="B13" s="1">
-        <v>7891033492503</v>
+        <v>53430</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="C13">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>49766</v>
-      </c>
-      <c r="B14" s="1">
-        <v>7891033497669</v>
+        <v>53500</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>49812</v>
-      </c>
-      <c r="B15" s="1">
-        <v>7891033498123</v>
+        <v>53501</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="C15">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>50418</v>
-      </c>
-      <c r="B16" s="1">
-        <v>7891033504183</v>
+        <v>53502</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="C16">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>50662</v>
-      </c>
-      <c r="B17" s="1">
-        <v>7891033506620</v>
+        <v>53504</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>50797</v>
-      </c>
-      <c r="B18" s="1">
-        <v>7891033507979</v>
+        <v>53506</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>50931</v>
-      </c>
-      <c r="B19" s="1">
-        <v>7891033509317</v>
+        <v>53519</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>51225</v>
-      </c>
-      <c r="B20" s="1">
-        <v>7891033512256</v>
+        <v>53520</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>21</v>
       </c>
       <c r="C20">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>51227</v>
-      </c>
-      <c r="B21" s="1">
-        <v>7891033512270</v>
+        <v>54887</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>22</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>51438</v>
-      </c>
-      <c r="B22" s="1">
-        <v>7891033514380</v>
+        <v>55669</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>51801</v>
-      </c>
-      <c r="B23" s="1">
-        <v>7891033518012</v>
+        <v>55802</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>51808</v>
-      </c>
-      <c r="B24" s="1">
-        <v>7891033518081</v>
+        <v>55803</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>52019</v>
-      </c>
-      <c r="B25" s="1">
-        <v>7891033520190</v>
+        <v>58119</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="C25">
         <v>4</v>
@@ -706,54 +931,54 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>52493</v>
-      </c>
-      <c r="B26" s="1">
-        <v>7891033524938</v>
+        <v>58120</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>52752</v>
-      </c>
-      <c r="B27" s="1">
-        <v>7891033527526</v>
+        <v>58121</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="C27">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>53096</v>
-      </c>
-      <c r="B28" s="1">
-        <v>7891033530960</v>
+        <v>58363</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="C28">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>53144</v>
-      </c>
-      <c r="B29" s="1">
-        <v>7891033531448</v>
+        <v>58845</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>30</v>
       </c>
       <c r="C29">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>53346</v>
-      </c>
-      <c r="B30" s="1">
-        <v>7891033533466</v>
+        <v>59132</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="C30">
         <v>2</v>
@@ -761,10 +986,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>53347</v>
-      </c>
-      <c r="B31" s="1">
-        <v>7891033533473</v>
+        <v>59823</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="C31">
         <v>2</v>
@@ -772,21 +997,21 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>53430</v>
-      </c>
-      <c r="B32" s="1">
-        <v>7891033534302</v>
+        <v>83684</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="C32">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>53437</v>
-      </c>
-      <c r="B33" s="1">
-        <v>7891033534371</v>
+        <v>84182</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="C33">
         <v>2</v>
@@ -794,32 +1019,32 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>53501</v>
-      </c>
-      <c r="B34" s="1">
-        <v>7891033535019</v>
+        <v>84213</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="C34">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>53921</v>
-      </c>
-      <c r="B35" s="1">
-        <v>7891033539215</v>
+        <v>85547</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="C35">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>53927</v>
-      </c>
-      <c r="B36" s="1">
-        <v>7891033539277</v>
+        <v>86225</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="C36">
         <v>2</v>
@@ -827,10 +1052,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>54101</v>
-      </c>
-      <c r="B37" s="1">
-        <v>7891033541010</v>
+        <v>86902</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="C37">
         <v>2</v>
@@ -838,21 +1063,21 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>55476</v>
-      </c>
-      <c r="B38" s="1">
-        <v>7891033554768</v>
+        <v>87108</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="C38">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>55675</v>
-      </c>
-      <c r="B39" s="1">
-        <v>7891033556755</v>
+        <v>87135</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="C39">
         <v>2</v>
@@ -860,98 +1085,98 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>55763</v>
-      </c>
-      <c r="B40" s="1">
-        <v>7891033557639</v>
+        <v>87328</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="C40">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>55803</v>
-      </c>
-      <c r="B41" s="1">
-        <v>7891033558032</v>
+        <v>88135</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="C41">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>55804</v>
-      </c>
-      <c r="B42" s="1">
-        <v>7891033558049</v>
+        <v>89679</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="C42">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>55805</v>
-      </c>
-      <c r="B43" s="1">
-        <v>7891033558056</v>
+        <v>89767</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="C43">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>55957</v>
-      </c>
-      <c r="B44" s="1">
-        <v>7891033559572</v>
+        <v>89816</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="C44">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>57882</v>
-      </c>
-      <c r="B45" s="1">
-        <v>7891033578825</v>
+        <v>90499</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="C45">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>58119</v>
-      </c>
-      <c r="B46" s="1">
-        <v>7891033581191</v>
+        <v>90501</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="C46">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>58120</v>
-      </c>
-      <c r="B47" s="1">
-        <v>7891033581207</v>
+        <v>90813</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="C47">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>58121</v>
-      </c>
-      <c r="B48" s="1">
-        <v>7891033581214</v>
+        <v>93542</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="C48">
         <v>3</v>
@@ -959,76 +1184,76 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>58122</v>
-      </c>
-      <c r="B49" s="1">
-        <v>7891033581221</v>
+        <v>94133</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="C49">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>59170</v>
-      </c>
-      <c r="B50" s="1">
-        <v>7891033591701</v>
+        <v>94134</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="C50">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>59823</v>
-      </c>
-      <c r="B51" s="1">
-        <v>7891033598236</v>
+        <v>94135</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="C51">
-        <v>6</v>
+        <v>107</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>70693</v>
-      </c>
-      <c r="B52" s="1">
-        <v>7891033706938</v>
+        <v>94138</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>53</v>
       </c>
       <c r="C52">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>76700</v>
-      </c>
-      <c r="B53" s="1">
-        <v>7891033767007</v>
+        <v>94139</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="C53">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>76756</v>
-      </c>
-      <c r="B54" s="1">
-        <v>7891033767564</v>
+        <v>94140</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="C54">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>78620</v>
-      </c>
-      <c r="B55" s="1">
-        <v>7891033786206</v>
+        <v>94141</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="C55">
         <v>3</v>
@@ -1036,76 +1261,76 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>82061</v>
-      </c>
-      <c r="B56" s="1">
-        <v>7891033820610</v>
+        <v>94142</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="C56">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>82685</v>
-      </c>
-      <c r="B57" s="1">
-        <v>7891033826858</v>
+        <v>94145</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="C57">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>84182</v>
-      </c>
-      <c r="B58" s="1">
-        <v>7891033841820</v>
+        <v>94147</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="C58">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>84213</v>
-      </c>
-      <c r="B59" s="1">
-        <v>7891033842131</v>
+        <v>94148</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="C59">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>84385</v>
-      </c>
-      <c r="B60" s="1">
-        <v>7891033843855</v>
+        <v>94149</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="C60">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>84388</v>
-      </c>
-      <c r="B61" s="1">
-        <v>7891033843886</v>
+        <v>94150</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="C61">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>84390</v>
-      </c>
-      <c r="B62" s="1">
-        <v>7891033843909</v>
+        <v>94154</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="C62">
         <v>8</v>
@@ -1113,10 +1338,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>85268</v>
-      </c>
-      <c r="B63" s="1">
-        <v>7891033852680</v>
+        <v>94155</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="C63">
         <v>2</v>
@@ -1124,10 +1349,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>85547</v>
-      </c>
-      <c r="B64" s="1">
-        <v>7891033855476</v>
+        <v>94156</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C64">
         <v>2</v>
@@ -1135,109 +1360,109 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>85564</v>
-      </c>
-      <c r="B65" s="1">
-        <v>7891033855643</v>
+        <v>94158</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="C65">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>86431</v>
-      </c>
-      <c r="B66" s="1">
-        <v>7891033864317</v>
+        <v>94159</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="C66">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>86432</v>
-      </c>
-      <c r="B67" s="1">
-        <v>7891033864324</v>
+        <v>94160</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="C67">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>86465</v>
-      </c>
-      <c r="B68" s="1">
-        <v>7891033864652</v>
+        <v>94305</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="C68">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>86759</v>
-      </c>
-      <c r="B69" s="1">
-        <v>7891033867592</v>
+        <v>94349</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="C69">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>86893</v>
-      </c>
-      <c r="B70" s="1">
-        <v>7891033868933</v>
+        <v>94401</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="C70">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>87135</v>
-      </c>
-      <c r="B71" s="1">
-        <v>7891033871353</v>
+        <v>94499</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="C71">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>87292</v>
-      </c>
-      <c r="B72" s="1">
-        <v>7891033872923</v>
+        <v>94525</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="C72">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>87340</v>
-      </c>
-      <c r="B73" s="1">
-        <v>7891033873401</v>
+        <v>94572</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="C73">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>87453</v>
-      </c>
-      <c r="B74" s="1">
-        <v>7891033874538</v>
+        <v>94574</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="C74">
         <v>5</v>
@@ -1245,311 +1470,52 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>87972</v>
-      </c>
-      <c r="B75" s="1">
-        <v>7891033879724</v>
+        <v>94576</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="C75">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>88135</v>
-      </c>
-      <c r="B76" s="1">
-        <v>7891033881352</v>
+        <v>94650</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="C76">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77">
-        <v>88303</v>
-      </c>
-      <c r="B77" s="1">
-        <v>7891033883035</v>
-      </c>
-      <c r="C77">
-        <v>2</v>
-      </c>
+      <c r="B77" s="1"/>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78">
-        <v>88364</v>
-      </c>
-      <c r="B78" s="1">
-        <v>7891033883646</v>
-      </c>
-      <c r="C78">
-        <v>2</v>
-      </c>
+      <c r="B78" s="1"/>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79">
-        <v>88687</v>
-      </c>
-      <c r="B79" s="1">
-        <v>7891033886876</v>
-      </c>
-      <c r="C79">
-        <v>2</v>
-      </c>
+      <c r="B79" s="1"/>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80">
-        <v>89281</v>
-      </c>
-      <c r="B80" s="1">
-        <v>7891033892815</v>
-      </c>
-      <c r="C80">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81">
-        <v>89642</v>
-      </c>
-      <c r="B81" s="1">
-        <v>7891033896424</v>
-      </c>
-      <c r="C81">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82">
-        <v>89678</v>
-      </c>
-      <c r="B82" s="1">
-        <v>7891033896783</v>
-      </c>
-      <c r="C82">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83">
-        <v>89679</v>
-      </c>
-      <c r="B83" s="1">
-        <v>7891033896790</v>
-      </c>
-      <c r="C83">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84">
-        <v>89680</v>
-      </c>
-      <c r="B84" s="1">
-        <v>7891033896806</v>
-      </c>
-      <c r="C84">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85">
-        <v>89715</v>
-      </c>
-      <c r="B85" s="1">
-        <v>7891033897155</v>
-      </c>
-      <c r="C85">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86">
-        <v>89767</v>
-      </c>
-      <c r="B86">
-        <v>7891033897674</v>
-      </c>
-      <c r="C86">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87">
-        <v>89816</v>
-      </c>
-      <c r="B87">
-        <v>7891033898169</v>
-      </c>
-      <c r="C87">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88">
-        <v>90810</v>
-      </c>
-      <c r="B88">
-        <v>7891033908103</v>
-      </c>
-      <c r="C88">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89">
-        <v>93063</v>
-      </c>
-      <c r="B89">
-        <v>7891033930630</v>
-      </c>
-      <c r="C89">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90">
-        <v>93065</v>
-      </c>
-      <c r="B90">
-        <v>7891033930654</v>
-      </c>
-      <c r="C90">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91">
-        <v>94154</v>
-      </c>
-      <c r="B91">
-        <v>7891033941544</v>
-      </c>
-      <c r="C91">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92">
-        <v>94155</v>
-      </c>
-      <c r="B92">
-        <v>7891033941551</v>
-      </c>
-      <c r="C92">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93">
-        <v>94161</v>
-      </c>
-      <c r="B93">
-        <v>7891033941612</v>
-      </c>
-      <c r="C93">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94">
-        <v>94162</v>
-      </c>
-      <c r="B94">
-        <v>7891033941629</v>
-      </c>
-      <c r="C94">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95">
-        <v>94305</v>
-      </c>
-      <c r="B95">
-        <v>7891033943050</v>
-      </c>
-      <c r="C95">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96">
-        <v>94401</v>
-      </c>
-      <c r="B96">
-        <v>7891033944019</v>
-      </c>
-      <c r="C96">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97">
-        <v>94499</v>
-      </c>
-      <c r="B97">
-        <v>7891033944996</v>
-      </c>
-      <c r="C97">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98">
-        <v>94525</v>
-      </c>
-      <c r="B98">
-        <v>7891033945252</v>
-      </c>
-      <c r="C98">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99">
-        <v>94851</v>
-      </c>
-      <c r="B99">
-        <v>7891033948512</v>
-      </c>
-      <c r="C99">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100">
-        <v>94852</v>
-      </c>
-      <c r="B100">
-        <v>7891033948529</v>
-      </c>
-      <c r="C100">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101">
-        <v>95496</v>
-      </c>
-      <c r="B101">
-        <v>7891033954964</v>
-      </c>
-      <c r="C101">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102">
-        <v>96617</v>
-      </c>
-      <c r="B102">
-        <v>7891033966172</v>
-      </c>
-      <c r="C102">
-        <v>9</v>
-      </c>
+      <c r="B80" s="1"/>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B81" s="1"/>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B82" s="1"/>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B83" s="1"/>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B84" s="1"/>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B85" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:C33" xr:uid="{14B8BA79-486A-4311-9DC6-50AF49FF2C77}"/>

--- a/Programa conferencia.xlsx
+++ b/Programa conferencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Apoio1\Desktop\sistema-conferencia-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22D2B14D-02E4-47AA-9840-DFA2AB22F040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB2D8B6-73D8-4AE1-9274-E38A778D7FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{D9876C19-AA45-4750-98F6-B6407576DC16}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>Código do Produto</t>
   </si>
@@ -53,229 +53,145 @@
     <t>Volumes</t>
   </si>
   <si>
-    <t>7891033016440</t>
-  </si>
-  <si>
-    <t>7891033129676</t>
-  </si>
-  <si>
-    <t>7891033471775</t>
-  </si>
-  <si>
-    <t>7891033474011</t>
-  </si>
-  <si>
-    <t>7891033498123</t>
-  </si>
-  <si>
-    <t>7891033512256</t>
-  </si>
-  <si>
-    <t>7891033512270</t>
-  </si>
-  <si>
-    <t>7891033518081</t>
-  </si>
-  <si>
-    <t>7891033520190</t>
-  </si>
-  <si>
-    <t>7891033520527</t>
-  </si>
-  <si>
-    <t>7891033521470</t>
-  </si>
-  <si>
-    <t>7891033534302</t>
-  </si>
-  <si>
-    <t>7891033535002</t>
-  </si>
-  <si>
-    <t>7891033535019</t>
-  </si>
-  <si>
-    <t>7891033535026</t>
-  </si>
-  <si>
-    <t>7891033535040</t>
-  </si>
-  <si>
-    <t>7891033535064</t>
-  </si>
-  <si>
-    <t>7891033535194</t>
-  </si>
-  <si>
-    <t>7891033535200</t>
-  </si>
-  <si>
     <t>7891033548873</t>
   </si>
   <si>
-    <t>7891033556694</t>
-  </si>
-  <si>
-    <t>7891033558025</t>
-  </si>
-  <si>
-    <t>7891033558032</t>
-  </si>
-  <si>
     <t>7891033581191</t>
   </si>
   <si>
-    <t>7891033581207</t>
-  </si>
-  <si>
-    <t>7891033581214</t>
-  </si>
-  <si>
-    <t>7891033583638</t>
-  </si>
-  <si>
-    <t>7891033588459</t>
-  </si>
-  <si>
-    <t>7891033591329</t>
-  </si>
-  <si>
-    <t>7891033598236</t>
-  </si>
-  <si>
-    <t>7891033836840</t>
-  </si>
-  <si>
-    <t>7891033841820</t>
-  </si>
-  <si>
-    <t>7891033842131</t>
-  </si>
-  <si>
-    <t>7891033855476</t>
-  </si>
-  <si>
-    <t>7891033862252</t>
-  </si>
-  <si>
-    <t>7891033869022</t>
-  </si>
-  <si>
-    <t>7891033871087</t>
-  </si>
-  <si>
-    <t>7891033871353</t>
-  </si>
-  <si>
-    <t>7891033873289</t>
-  </si>
-  <si>
-    <t>7891033881352</t>
-  </si>
-  <si>
-    <t>7891033896790</t>
-  </si>
-  <si>
-    <t>7891033897674</t>
-  </si>
-  <si>
-    <t>7891033898169</t>
-  </si>
-  <si>
     <t>7891033904990</t>
   </si>
   <si>
-    <t>7891033905010</t>
-  </si>
-  <si>
-    <t>7891033908134</t>
-  </si>
-  <si>
-    <t>7891033935420</t>
-  </si>
-  <si>
-    <t>7891033941339</t>
-  </si>
-  <si>
-    <t>7891033941346</t>
-  </si>
-  <si>
-    <t>7891033941353</t>
-  </si>
-  <si>
-    <t>7891033941384</t>
-  </si>
-  <si>
-    <t>7891033941391</t>
-  </si>
-  <si>
-    <t>7891033941407</t>
-  </si>
-  <si>
-    <t>7891033941414</t>
-  </si>
-  <si>
     <t>7891033941421</t>
   </si>
   <si>
-    <t>7891033941452</t>
-  </si>
-  <si>
-    <t>7891033941476</t>
-  </si>
-  <si>
-    <t>7891033941483</t>
-  </si>
-  <si>
-    <t>7891033941490</t>
-  </si>
-  <si>
-    <t>7891033941506</t>
-  </si>
-  <si>
-    <t>7891033941544</t>
-  </si>
-  <si>
     <t>7891033941551</t>
   </si>
   <si>
-    <t>7891033941568</t>
-  </si>
-  <si>
-    <t>7891033941582</t>
-  </si>
-  <si>
-    <t>7891033941599</t>
-  </si>
-  <si>
-    <t>7891033941605</t>
-  </si>
-  <si>
-    <t>7891033943050</t>
-  </si>
-  <si>
-    <t>7891033943494</t>
-  </si>
-  <si>
-    <t>7891033944019</t>
-  </si>
-  <si>
-    <t>7891033944996</t>
-  </si>
-  <si>
-    <t>7891033945252</t>
-  </si>
-  <si>
-    <t>7891033945726</t>
-  </si>
-  <si>
-    <t>7891033945740</t>
-  </si>
-  <si>
-    <t>7891033945764</t>
-  </si>
-  <si>
-    <t>7891033946501</t>
+    <t>7891033483075</t>
+  </si>
+  <si>
+    <t>7891033492473</t>
+  </si>
+  <si>
+    <t>7891033507320</t>
+  </si>
+  <si>
+    <t>7891033511235</t>
+  </si>
+  <si>
+    <t>7891033512447</t>
+  </si>
+  <si>
+    <t>7891033525072</t>
+  </si>
+  <si>
+    <t>7891033583928</t>
+  </si>
+  <si>
+    <t>7891033590193</t>
+  </si>
+  <si>
+    <t>7891033594665</t>
+  </si>
+  <si>
+    <t>7891033597208</t>
+  </si>
+  <si>
+    <t>7891033741038</t>
+  </si>
+  <si>
+    <t>7891033826896</t>
+  </si>
+  <si>
+    <t>7891033826902</t>
+  </si>
+  <si>
+    <t>7891033856060</t>
+  </si>
+  <si>
+    <t>7891033868094</t>
+  </si>
+  <si>
+    <t>7891033869909</t>
+  </si>
+  <si>
+    <t>7891033875320</t>
+  </si>
+  <si>
+    <t>7891033878963</t>
+  </si>
+  <si>
+    <t>7891033880829</t>
+  </si>
+  <si>
+    <t>7891033886883</t>
+  </si>
+  <si>
+    <t>7891033886920</t>
+  </si>
+  <si>
+    <t>7891033894222</t>
+  </si>
+  <si>
+    <t>7891033896783</t>
+  </si>
+  <si>
+    <t>7891033908066</t>
+  </si>
+  <si>
+    <t>7891033909858</t>
+  </si>
+  <si>
+    <t>7891033941360</t>
+  </si>
+  <si>
+    <t>7891033941377</t>
+  </si>
+  <si>
+    <t>7891033941612</t>
+  </si>
+  <si>
+    <t>7891033943074</t>
+  </si>
+  <si>
+    <t>7891033943081</t>
+  </si>
+  <si>
+    <t>7891033944798</t>
+  </si>
+  <si>
+    <t>7891033944897</t>
+  </si>
+  <si>
+    <t>7891033946617</t>
+  </si>
+  <si>
+    <t>7891033946624</t>
+  </si>
+  <si>
+    <t>7891033946631</t>
+  </si>
+  <si>
+    <t>7891033946648</t>
+  </si>
+  <si>
+    <t>7891033946655</t>
+  </si>
+  <si>
+    <t>7891033946662</t>
+  </si>
+  <si>
+    <t>7891033946679</t>
+  </si>
+  <si>
+    <t>7891033946723</t>
+  </si>
+  <si>
+    <t>7891033956753</t>
+  </si>
+  <si>
+    <t>7891033970063</t>
   </si>
 </sst>
 </file>
@@ -667,21 +583,21 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>1644</v>
+        <v>48307</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>12967</v>
+        <v>49247</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -689,359 +605,359 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>47177</v>
+        <v>50732</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>47401</v>
+        <v>51123</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>49812</v>
+        <v>51244</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>51225</v>
+        <v>52507</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>51227</v>
+        <v>54887</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>51808</v>
+        <v>58119</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>52019</v>
+        <v>58392</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>52052</v>
+        <v>59019</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>52147</v>
+        <v>59466</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C12">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>53430</v>
+        <v>59720</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>53500</v>
+        <v>74103</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>53501</v>
+        <v>82689</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C15">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>53502</v>
+        <v>82690</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C16">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>53504</v>
+        <v>85606</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>53506</v>
+        <v>86809</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C18">
-        <v>22</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>53519</v>
+        <v>86990</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C19">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>53520</v>
+        <v>87532</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>54887</v>
+        <v>87896</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C21">
-        <v>4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>55669</v>
+        <v>88082</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C22">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>55802</v>
+        <v>88688</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C23">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>55803</v>
+        <v>88692</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>58119</v>
+        <v>89422</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C25">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>58120</v>
+        <v>89678</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C26">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>58121</v>
+        <v>90499</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>58363</v>
+        <v>90806</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>58845</v>
+        <v>90985</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C29">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>59132</v>
+        <v>94136</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C30">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>59823</v>
+        <v>94137</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>83684</v>
+        <v>94142</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>84182</v>
+        <v>94155</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>84213</v>
+        <v>94161</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>35</v>
       </c>
       <c r="C34">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>85547</v>
+        <v>94307</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>36</v>
       </c>
       <c r="C35">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>86225</v>
+        <v>94308</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>37</v>
@@ -1052,51 +968,51 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>86902</v>
+        <v>94479</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>38</v>
       </c>
       <c r="C37">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>87108</v>
+        <v>94489</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>39</v>
       </c>
       <c r="C38">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>87135</v>
+        <v>94661</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>40</v>
       </c>
       <c r="C39">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>87328</v>
+        <v>94662</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>41</v>
       </c>
       <c r="C40">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>88135</v>
+        <v>94663</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>42</v>
@@ -1107,399 +1023,175 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>89679</v>
+        <v>94664</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>43</v>
       </c>
       <c r="C42">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>89767</v>
+        <v>94665</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>44</v>
       </c>
       <c r="C43">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>89816</v>
+        <v>94666</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>45</v>
       </c>
       <c r="C44">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>90499</v>
+        <v>94667</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C45">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>90501</v>
+        <v>94672</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>47</v>
       </c>
       <c r="C46">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>90813</v>
+        <v>95675</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>48</v>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>93542</v>
+        <v>97006</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C48">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>94133</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C49">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>94134</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C50">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>94135</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C51">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>94138</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C52">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>94139</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C53">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>94140</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C54">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>94141</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C55">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>94142</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C56">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>94145</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C57">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>94147</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C58">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>94148</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C59">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60">
-        <v>94149</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C60">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61">
-        <v>94150</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C61">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>94154</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C62">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <v>94155</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C63">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64">
-        <v>94156</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C64">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>94158</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C65">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66">
-        <v>94159</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C66">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>94160</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C67">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>94305</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C68">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69">
-        <v>94349</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C69">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>94401</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C70">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71">
-        <v>94499</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C71">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <v>94525</v>
-      </c>
-      <c r="B72" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C72">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73">
-        <v>94572</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C73">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74">
-        <v>94574</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C74">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75">
-        <v>94576</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C75">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76">
-        <v>94650</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C76">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B49" s="1"/>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B50" s="1"/>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B51" s="1"/>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B52" s="1"/>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B53" s="1"/>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B54" s="1"/>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B55" s="1"/>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B56" s="1"/>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B57" s="1"/>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B58" s="1"/>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B59" s="1"/>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B60" s="1"/>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B61" s="1"/>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B62" s="1"/>
+    </row>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B63" s="1"/>
+    </row>
+    <row r="64" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B64" s="1"/>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B65" s="1"/>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B66" s="1"/>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B67" s="1"/>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B68" s="1"/>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B69" s="1"/>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B70" s="1"/>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B71" s="1"/>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B72" s="1"/>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B73" s="1"/>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B74" s="1"/>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B75" s="1"/>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B76" s="1"/>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B77" s="1"/>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B78" s="1"/>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B79" s="1"/>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B80" s="1"/>
     </row>
     <row r="81" spans="2:2" x14ac:dyDescent="0.25">

--- a/Programa conferencia.xlsx
+++ b/Programa conferencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Apoio1\Desktop\sistema-conferencia-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BB2D8B6-73D8-4AE1-9274-E38A778D7FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C54C69-AB37-4F1D-B1ED-620EE2C40CA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{D9876C19-AA45-4750-98F6-B6407576DC16}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="180">
   <si>
     <t>Código do Produto</t>
   </si>
@@ -192,6 +192,396 @@
   </si>
   <si>
     <t>7891033970063</t>
+  </si>
+  <si>
+    <t>7891033013029</t>
+  </si>
+  <si>
+    <t>7891033013142</t>
+  </si>
+  <si>
+    <t>7891033013173</t>
+  </si>
+  <si>
+    <t>7891033050093</t>
+  </si>
+  <si>
+    <t>7891033051250</t>
+  </si>
+  <si>
+    <t>7891033198160</t>
+  </si>
+  <si>
+    <t>7891033471775</t>
+  </si>
+  <si>
+    <t>7891033478880</t>
+  </si>
+  <si>
+    <t>7891033483037</t>
+  </si>
+  <si>
+    <t>7891033483150</t>
+  </si>
+  <si>
+    <t>7891033486533</t>
+  </si>
+  <si>
+    <t>7891033490257</t>
+  </si>
+  <si>
+    <t>7891033491544</t>
+  </si>
+  <si>
+    <t>7891033491933</t>
+  </si>
+  <si>
+    <t>7891033499441</t>
+  </si>
+  <si>
+    <t>7891033500147</t>
+  </si>
+  <si>
+    <t>7891033500222</t>
+  </si>
+  <si>
+    <t>7891033501250</t>
+  </si>
+  <si>
+    <t>7891033502684</t>
+  </si>
+  <si>
+    <t>7891033504183</t>
+  </si>
+  <si>
+    <t>7891033506774</t>
+  </si>
+  <si>
+    <t>7891033508822</t>
+  </si>
+  <si>
+    <t>7891033509317</t>
+  </si>
+  <si>
+    <t>7891033511655</t>
+  </si>
+  <si>
+    <t>7891033512256</t>
+  </si>
+  <si>
+    <t>7891033512270</t>
+  </si>
+  <si>
+    <t>7891033512393</t>
+  </si>
+  <si>
+    <t>7891033514366</t>
+  </si>
+  <si>
+    <t>7891033514410</t>
+  </si>
+  <si>
+    <t>7891033517046</t>
+  </si>
+  <si>
+    <t>7891033518012</t>
+  </si>
+  <si>
+    <t>7891033518081</t>
+  </si>
+  <si>
+    <t>7891033520190</t>
+  </si>
+  <si>
+    <t>7891033520442</t>
+  </si>
+  <si>
+    <t>7891033521104</t>
+  </si>
+  <si>
+    <t>7891033521401</t>
+  </si>
+  <si>
+    <t>7891033521685</t>
+  </si>
+  <si>
+    <t>7891033521906</t>
+  </si>
+  <si>
+    <t>7891033525911</t>
+  </si>
+  <si>
+    <t>7891033527526</t>
+  </si>
+  <si>
+    <t>7891033530953</t>
+  </si>
+  <si>
+    <t>7891033531448</t>
+  </si>
+  <si>
+    <t>7891033533466</t>
+  </si>
+  <si>
+    <t>7891033533473</t>
+  </si>
+  <si>
+    <t>7891033534524</t>
+  </si>
+  <si>
+    <t>7891033535019</t>
+  </si>
+  <si>
+    <t>7891033535026</t>
+  </si>
+  <si>
+    <t>7891033535040</t>
+  </si>
+  <si>
+    <t>7891033535064</t>
+  </si>
+  <si>
+    <t>7891033538355</t>
+  </si>
+  <si>
+    <t>7891033539222</t>
+  </si>
+  <si>
+    <t>7891033543601</t>
+  </si>
+  <si>
+    <t>7891033546572</t>
+  </si>
+  <si>
+    <t>7891033546589</t>
+  </si>
+  <si>
+    <t>7891033550838</t>
+  </si>
+  <si>
+    <t>7891033554744</t>
+  </si>
+  <si>
+    <t>7891033554881</t>
+  </si>
+  <si>
+    <t>7891033556694</t>
+  </si>
+  <si>
+    <t>7891033556762</t>
+  </si>
+  <si>
+    <t>7891033557639</t>
+  </si>
+  <si>
+    <t>7891033558025</t>
+  </si>
+  <si>
+    <t>7891033558032</t>
+  </si>
+  <si>
+    <t>7891033558056</t>
+  </si>
+  <si>
+    <t>7891033559572</t>
+  </si>
+  <si>
+    <t>7891033559589</t>
+  </si>
+  <si>
+    <t>7891033566013</t>
+  </si>
+  <si>
+    <t>7891033566860</t>
+  </si>
+  <si>
+    <t>7891033570423</t>
+  </si>
+  <si>
+    <t>7891033575503</t>
+  </si>
+  <si>
+    <t>7891033575978</t>
+  </si>
+  <si>
+    <t>7891033581207</t>
+  </si>
+  <si>
+    <t>7891033581214</t>
+  </si>
+  <si>
+    <t>7891033583072</t>
+  </si>
+  <si>
+    <t>7891033583089</t>
+  </si>
+  <si>
+    <t>7891033583102</t>
+  </si>
+  <si>
+    <t>7891033583577</t>
+  </si>
+  <si>
+    <t>7891033585267</t>
+  </si>
+  <si>
+    <t>7891033586448</t>
+  </si>
+  <si>
+    <t>7891033587292</t>
+  </si>
+  <si>
+    <t>7891033589784</t>
+  </si>
+  <si>
+    <t>7891033589807</t>
+  </si>
+  <si>
+    <t>7891033594368</t>
+  </si>
+  <si>
+    <t>7891033598458</t>
+  </si>
+  <si>
+    <t>7891033733675</t>
+  </si>
+  <si>
+    <t>7891033744381</t>
+  </si>
+  <si>
+    <t>7891033757718</t>
+  </si>
+  <si>
+    <t>7891033818495</t>
+  </si>
+  <si>
+    <t>7891033826858</t>
+  </si>
+  <si>
+    <t>7891033826865</t>
+  </si>
+  <si>
+    <t>7891033826889</t>
+  </si>
+  <si>
+    <t>7891033831456</t>
+  </si>
+  <si>
+    <t>7891033836840</t>
+  </si>
+  <si>
+    <t>7891033841134</t>
+  </si>
+  <si>
+    <t>7891033842148</t>
+  </si>
+  <si>
+    <t>7891033843855</t>
+  </si>
+  <si>
+    <t>7891033843916</t>
+  </si>
+  <si>
+    <t>7891033843923</t>
+  </si>
+  <si>
+    <t>7891033853083</t>
+  </si>
+  <si>
+    <t>7891033853694</t>
+  </si>
+  <si>
+    <t>7891033855643</t>
+  </si>
+  <si>
+    <t>7891033861675</t>
+  </si>
+  <si>
+    <t>7891033862252</t>
+  </si>
+  <si>
+    <t>7891033864324</t>
+  </si>
+  <si>
+    <t>7891033864652</t>
+  </si>
+  <si>
+    <t>7891033868759</t>
+  </si>
+  <si>
+    <t>7891033868933</t>
+  </si>
+  <si>
+    <t>7891033870646</t>
+  </si>
+  <si>
+    <t>7891033871261</t>
+  </si>
+  <si>
+    <t>7891033871322</t>
+  </si>
+  <si>
+    <t>7891033871353</t>
+  </si>
+  <si>
+    <t>7891033871438</t>
+  </si>
+  <si>
+    <t>7891033872916</t>
+  </si>
+  <si>
+    <t>7891033873401</t>
+  </si>
+  <si>
+    <t>7891033875573</t>
+  </si>
+  <si>
+    <t>7891033875597</t>
+  </si>
+  <si>
+    <t>7891033878079</t>
+  </si>
+  <si>
+    <t>7891033878987</t>
+  </si>
+  <si>
+    <t>7891033879724</t>
+  </si>
+  <si>
+    <t>7891033886227</t>
+  </si>
+  <si>
+    <t>7891033896790</t>
+  </si>
+  <si>
+    <t>7891033903108</t>
+  </si>
+  <si>
+    <t>7891033908080</t>
+  </si>
+  <si>
+    <t>7891033909247</t>
+  </si>
+  <si>
+    <t>7891033909841</t>
+  </si>
+  <si>
+    <t>7891033909872</t>
+  </si>
+  <si>
+    <t>7891033917211</t>
+  </si>
+  <si>
+    <t>7891033930470</t>
+  </si>
+  <si>
+    <t>7891033944996</t>
+  </si>
+  <si>
+    <t>7891033945726</t>
+  </si>
+  <si>
+    <t>7891033977277</t>
   </si>
 </sst>
 </file>
@@ -564,7 +954,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14B8BA79-486A-4311-9DC6-50AF49FF2C77}">
-  <dimension ref="A1:C85"/>
+  <dimension ref="A1:C178"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
@@ -583,21 +973,21 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>48307</v>
+        <v>1302</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="C2">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>49247</v>
+        <v>1314</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -605,153 +995,153 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>50732</v>
+        <v>1317</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>51123</v>
+        <v>5009</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>51244</v>
+        <v>5125</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>52507</v>
+        <v>19816</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7">
         <v>13</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>54887</v>
+        <v>47177</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>58119</v>
+        <v>47888</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>58392</v>
+        <v>48303</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="C10">
-        <v>5</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>59019</v>
+        <v>48307</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C11">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>59466</v>
+        <v>48315</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="C12">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>59720</v>
+        <v>48653</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>74103</v>
+        <v>49025</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="C14">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>82689</v>
+        <v>49154</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="C15">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>82690</v>
+        <v>49193</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="C16">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>85606</v>
+        <v>49247</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C17">
         <v>2</v>
@@ -759,455 +1149,1774 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>86809</v>
+        <v>49944</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>22</v>
+        <v>64</v>
       </c>
       <c r="C18">
-        <v>74</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>86990</v>
+        <v>50014</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="C19">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>87532</v>
+        <v>50022</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="C20">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>87896</v>
+        <v>50125</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="C21">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>88082</v>
+        <v>50268</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="C22">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
-        <v>88688</v>
+        <v>50418</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="C23">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>88692</v>
+        <v>50677</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="C24">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>89422</v>
+        <v>50732</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>89678</v>
+        <v>50882</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="C26">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>90499</v>
+        <v>50931</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="C27">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>90806</v>
+        <v>51123</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C28">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>90985</v>
+        <v>51165</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="C29">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
-        <v>94136</v>
+        <v>51225</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="C30">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
-        <v>94137</v>
+        <v>51227</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="C31">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
-        <v>94142</v>
+        <v>51239</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="C32">
-        <v>13</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>94155</v>
+        <v>51244</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C33">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>94161</v>
+        <v>51436</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="C34">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
-        <v>94307</v>
+        <v>51441</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="C35">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>94308</v>
+        <v>51704</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="C36">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>94479</v>
+        <v>51801</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="C37">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>94489</v>
+        <v>51808</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>39</v>
+        <v>81</v>
       </c>
       <c r="C38">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>94661</v>
+        <v>52019</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="C39">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>94662</v>
+        <v>52044</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="C40">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>94663</v>
+        <v>52110</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="C41">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>94664</v>
+        <v>52140</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="C42">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>94665</v>
+        <v>52168</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>44</v>
+        <v>86</v>
       </c>
       <c r="C43">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>94666</v>
+        <v>52190</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="C44">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
-        <v>94667</v>
+        <v>52507</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="C45">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>94672</v>
+        <v>52591</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="C46">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>95675</v>
+        <v>52752</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>48</v>
+        <v>89</v>
       </c>
       <c r="C47">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
+        <v>53095</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>53144</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>53346</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C50">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>53347</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C51">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>53452</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>53501</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C53">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53502</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C54">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>53504</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C55">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>53506</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C56">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>53835</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C57">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>53922</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>54360</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>54657</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C60">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>54658</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>54887</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C62">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>55083</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>55474</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C64">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>55488</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>55669</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C66">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>55676</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C67">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>55763</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>55802</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C69">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>55803</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C70">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>55805</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C71">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>55957</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C72">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>55958</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C73">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>56601</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C74">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>56686</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>57042</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C76">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>57550</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>57597</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C78">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>58119</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C79">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>58120</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C80">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>58121</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C81">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>58307</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C82">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>58308</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C83">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>58310</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>58357</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C85">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>58392</v>
+      </c>
+      <c r="B86" t="s">
+        <v>14</v>
+      </c>
+      <c r="C86">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>58526</v>
+      </c>
+      <c r="B87" t="s">
+        <v>126</v>
+      </c>
+      <c r="C87">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>58644</v>
+      </c>
+      <c r="B88" t="s">
+        <v>127</v>
+      </c>
+      <c r="C88">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>58729</v>
+      </c>
+      <c r="B89" t="s">
+        <v>128</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>58978</v>
+      </c>
+      <c r="B90" t="s">
+        <v>129</v>
+      </c>
+      <c r="C90">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>58980</v>
+      </c>
+      <c r="B91" t="s">
+        <v>130</v>
+      </c>
+      <c r="C91">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>59019</v>
+      </c>
+      <c r="B92" t="s">
+        <v>15</v>
+      </c>
+      <c r="C92">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>59436</v>
+      </c>
+      <c r="B93" t="s">
+        <v>131</v>
+      </c>
+      <c r="C93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>59466</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>59720</v>
+      </c>
+      <c r="B95" t="s">
+        <v>17</v>
+      </c>
+      <c r="C95">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>59845</v>
+      </c>
+      <c r="B96" t="s">
+        <v>132</v>
+      </c>
+      <c r="C96">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>73367</v>
+      </c>
+      <c r="B97" t="s">
+        <v>133</v>
+      </c>
+      <c r="C97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>74103</v>
+      </c>
+      <c r="B98" t="s">
+        <v>18</v>
+      </c>
+      <c r="C98">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>74438</v>
+      </c>
+      <c r="B99" t="s">
+        <v>134</v>
+      </c>
+      <c r="C99">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>75771</v>
+      </c>
+      <c r="B100" t="s">
+        <v>135</v>
+      </c>
+      <c r="C100">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>81849</v>
+      </c>
+      <c r="B101" t="s">
+        <v>136</v>
+      </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>82685</v>
+      </c>
+      <c r="B102" t="s">
+        <v>137</v>
+      </c>
+      <c r="C102">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>82686</v>
+      </c>
+      <c r="B103" t="s">
+        <v>138</v>
+      </c>
+      <c r="C103">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>82688</v>
+      </c>
+      <c r="B104" t="s">
+        <v>139</v>
+      </c>
+      <c r="C104">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>82689</v>
+      </c>
+      <c r="B105" t="s">
+        <v>19</v>
+      </c>
+      <c r="C105">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>82690</v>
+      </c>
+      <c r="B106" t="s">
+        <v>20</v>
+      </c>
+      <c r="C106">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>83145</v>
+      </c>
+      <c r="B107" t="s">
+        <v>140</v>
+      </c>
+      <c r="C107">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>83684</v>
+      </c>
+      <c r="B108" t="s">
+        <v>141</v>
+      </c>
+      <c r="C108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>84113</v>
+      </c>
+      <c r="B109" t="s">
+        <v>142</v>
+      </c>
+      <c r="C109">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>84214</v>
+      </c>
+      <c r="B110" t="s">
+        <v>143</v>
+      </c>
+      <c r="C110">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>84385</v>
+      </c>
+      <c r="B111" t="s">
+        <v>144</v>
+      </c>
+      <c r="C111">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>84391</v>
+      </c>
+      <c r="B112" t="s">
+        <v>145</v>
+      </c>
+      <c r="C112">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>84392</v>
+      </c>
+      <c r="B113" t="s">
+        <v>146</v>
+      </c>
+      <c r="C113">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>85308</v>
+      </c>
+      <c r="B114" t="s">
+        <v>147</v>
+      </c>
+      <c r="C114">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>85369</v>
+      </c>
+      <c r="B115" t="s">
+        <v>148</v>
+      </c>
+      <c r="C115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>85564</v>
+      </c>
+      <c r="B116" t="s">
+        <v>149</v>
+      </c>
+      <c r="C116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>85606</v>
+      </c>
+      <c r="B117" t="s">
+        <v>21</v>
+      </c>
+      <c r="C117">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>86167</v>
+      </c>
+      <c r="B118" t="s">
+        <v>150</v>
+      </c>
+      <c r="C118">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>86225</v>
+      </c>
+      <c r="B119" t="s">
+        <v>151</v>
+      </c>
+      <c r="C119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>86432</v>
+      </c>
+      <c r="B120" t="s">
+        <v>152</v>
+      </c>
+      <c r="C120">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>86465</v>
+      </c>
+      <c r="B121" t="s">
+        <v>153</v>
+      </c>
+      <c r="C121">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122">
+        <v>86809</v>
+      </c>
+      <c r="B122" t="s">
+        <v>22</v>
+      </c>
+      <c r="C122">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123">
+        <v>86875</v>
+      </c>
+      <c r="B123" t="s">
+        <v>154</v>
+      </c>
+      <c r="C123">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124">
+        <v>86893</v>
+      </c>
+      <c r="B124" t="s">
+        <v>155</v>
+      </c>
+      <c r="C124">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125">
+        <v>86990</v>
+      </c>
+      <c r="B125" t="s">
+        <v>23</v>
+      </c>
+      <c r="C125">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126">
+        <v>87064</v>
+      </c>
+      <c r="B126" t="s">
+        <v>156</v>
+      </c>
+      <c r="C126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127">
+        <v>87126</v>
+      </c>
+      <c r="B127" t="s">
+        <v>157</v>
+      </c>
+      <c r="C127">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128">
+        <v>87132</v>
+      </c>
+      <c r="B128" t="s">
+        <v>158</v>
+      </c>
+      <c r="C128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129">
+        <v>87135</v>
+      </c>
+      <c r="B129" t="s">
+        <v>159</v>
+      </c>
+      <c r="C129">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130">
+        <v>87143</v>
+      </c>
+      <c r="B130" t="s">
+        <v>160</v>
+      </c>
+      <c r="C130">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131">
+        <v>87291</v>
+      </c>
+      <c r="B131" t="s">
+        <v>161</v>
+      </c>
+      <c r="C131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132">
+        <v>87340</v>
+      </c>
+      <c r="B132" t="s">
+        <v>162</v>
+      </c>
+      <c r="C132">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133">
+        <v>87532</v>
+      </c>
+      <c r="B133" t="s">
+        <v>24</v>
+      </c>
+      <c r="C133">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134">
+        <v>87557</v>
+      </c>
+      <c r="B134" t="s">
+        <v>163</v>
+      </c>
+      <c r="C134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135">
+        <v>87559</v>
+      </c>
+      <c r="B135" t="s">
+        <v>164</v>
+      </c>
+      <c r="C135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136">
+        <v>87807</v>
+      </c>
+      <c r="B136" t="s">
+        <v>165</v>
+      </c>
+      <c r="C136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137">
+        <v>87896</v>
+      </c>
+      <c r="B137" t="s">
+        <v>25</v>
+      </c>
+      <c r="C137">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138">
+        <v>87898</v>
+      </c>
+      <c r="B138" t="s">
+        <v>166</v>
+      </c>
+      <c r="C138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139">
+        <v>87972</v>
+      </c>
+      <c r="B139" t="s">
+        <v>167</v>
+      </c>
+      <c r="C139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140">
+        <v>88082</v>
+      </c>
+      <c r="B140" t="s">
+        <v>26</v>
+      </c>
+      <c r="C140">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141">
+        <v>88622</v>
+      </c>
+      <c r="B141" t="s">
+        <v>168</v>
+      </c>
+      <c r="C141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142">
+        <v>88688</v>
+      </c>
+      <c r="B142" t="s">
+        <v>27</v>
+      </c>
+      <c r="C142">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143">
+        <v>88692</v>
+      </c>
+      <c r="B143" t="s">
+        <v>28</v>
+      </c>
+      <c r="C143">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144">
+        <v>89422</v>
+      </c>
+      <c r="B144" t="s">
+        <v>29</v>
+      </c>
+      <c r="C144">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145">
+        <v>89678</v>
+      </c>
+      <c r="B145" t="s">
+        <v>30</v>
+      </c>
+      <c r="C145">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146">
+        <v>89679</v>
+      </c>
+      <c r="B146" t="s">
+        <v>169</v>
+      </c>
+      <c r="C146">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147">
+        <v>90310</v>
+      </c>
+      <c r="B147" t="s">
+        <v>170</v>
+      </c>
+      <c r="C147">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148">
+        <v>90499</v>
+      </c>
+      <c r="B148" t="s">
+        <v>5</v>
+      </c>
+      <c r="C148">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149">
+        <v>90806</v>
+      </c>
+      <c r="B149" t="s">
+        <v>31</v>
+      </c>
+      <c r="C149">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150">
+        <v>90808</v>
+      </c>
+      <c r="B150" t="s">
+        <v>171</v>
+      </c>
+      <c r="C150">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151">
+        <v>90924</v>
+      </c>
+      <c r="B151" t="s">
+        <v>172</v>
+      </c>
+      <c r="C151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152">
+        <v>90984</v>
+      </c>
+      <c r="B152" t="s">
+        <v>173</v>
+      </c>
+      <c r="C152">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153">
+        <v>90985</v>
+      </c>
+      <c r="B153" t="s">
+        <v>32</v>
+      </c>
+      <c r="C153">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154">
+        <v>90987</v>
+      </c>
+      <c r="B154" t="s">
+        <v>174</v>
+      </c>
+      <c r="C154">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155">
+        <v>91721</v>
+      </c>
+      <c r="B155" t="s">
+        <v>175</v>
+      </c>
+      <c r="C155">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156">
+        <v>93047</v>
+      </c>
+      <c r="B156" t="s">
+        <v>176</v>
+      </c>
+      <c r="C156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157">
+        <v>94136</v>
+      </c>
+      <c r="B157" t="s">
+        <v>33</v>
+      </c>
+      <c r="C157">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158">
+        <v>94137</v>
+      </c>
+      <c r="B158" t="s">
+        <v>34</v>
+      </c>
+      <c r="C158">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159">
+        <v>94142</v>
+      </c>
+      <c r="B159" t="s">
+        <v>6</v>
+      </c>
+      <c r="C159">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160">
+        <v>94155</v>
+      </c>
+      <c r="B160" t="s">
+        <v>7</v>
+      </c>
+      <c r="C160">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161">
+        <v>94161</v>
+      </c>
+      <c r="B161" t="s">
+        <v>35</v>
+      </c>
+      <c r="C161">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162">
+        <v>94307</v>
+      </c>
+      <c r="B162" t="s">
+        <v>36</v>
+      </c>
+      <c r="C162">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163">
+        <v>94308</v>
+      </c>
+      <c r="B163" t="s">
+        <v>37</v>
+      </c>
+      <c r="C163">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164">
+        <v>94479</v>
+      </c>
+      <c r="B164" t="s">
+        <v>38</v>
+      </c>
+      <c r="C164">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165">
+        <v>94489</v>
+      </c>
+      <c r="B165" t="s">
+        <v>39</v>
+      </c>
+      <c r="C165">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166">
+        <v>94499</v>
+      </c>
+      <c r="B166" t="s">
+        <v>177</v>
+      </c>
+      <c r="C166">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167">
+        <v>94572</v>
+      </c>
+      <c r="B167" t="s">
+        <v>178</v>
+      </c>
+      <c r="C167">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168">
+        <v>94661</v>
+      </c>
+      <c r="B168" t="s">
+        <v>40</v>
+      </c>
+      <c r="C168">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169">
+        <v>94662</v>
+      </c>
+      <c r="B169" t="s">
+        <v>41</v>
+      </c>
+      <c r="C169">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170">
+        <v>94663</v>
+      </c>
+      <c r="B170" t="s">
+        <v>42</v>
+      </c>
+      <c r="C170">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171">
+        <v>94664</v>
+      </c>
+      <c r="B171" t="s">
+        <v>43</v>
+      </c>
+      <c r="C171">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172">
+        <v>94665</v>
+      </c>
+      <c r="B172" t="s">
+        <v>44</v>
+      </c>
+      <c r="C172">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173">
+        <v>94666</v>
+      </c>
+      <c r="B173" t="s">
+        <v>45</v>
+      </c>
+      <c r="C173">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174">
+        <v>94667</v>
+      </c>
+      <c r="B174" t="s">
+        <v>46</v>
+      </c>
+      <c r="C174">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175">
+        <v>94672</v>
+      </c>
+      <c r="B175" t="s">
+        <v>47</v>
+      </c>
+      <c r="C175">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176">
+        <v>95675</v>
+      </c>
+      <c r="B176" t="s">
+        <v>48</v>
+      </c>
+      <c r="C176">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177">
         <v>97006</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B177" t="s">
         <v>49</v>
       </c>
-      <c r="C48">
+      <c r="C177">
         <v>49</v>
       </c>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B49" s="1"/>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B50" s="1"/>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B51" s="1"/>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B52" s="1"/>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B53" s="1"/>
-    </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B54" s="1"/>
-    </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B55" s="1"/>
-    </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B56" s="1"/>
-    </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B57" s="1"/>
-    </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B58" s="1"/>
-    </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B59" s="1"/>
-    </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B60" s="1"/>
-    </row>
-    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B61" s="1"/>
-    </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B62" s="1"/>
-    </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B63" s="1"/>
-    </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B64" s="1"/>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B65" s="1"/>
-    </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B66" s="1"/>
-    </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B67" s="1"/>
-    </row>
-    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B68" s="1"/>
-    </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B69" s="1"/>
-    </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B70" s="1"/>
-    </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B71" s="1"/>
-    </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B72" s="1"/>
-    </row>
-    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B73" s="1"/>
-    </row>
-    <row r="74" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B74" s="1"/>
-    </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B75" s="1"/>
-    </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B76" s="1"/>
-    </row>
-    <row r="77" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B77" s="1"/>
-    </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B78" s="1"/>
-    </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B79" s="1"/>
-    </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B80" s="1"/>
-    </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B81" s="1"/>
-    </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B82" s="1"/>
-    </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B83" s="1"/>
-    </row>
-    <row r="84" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B84" s="1"/>
-    </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B85" s="1"/>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178">
+        <v>97727</v>
+      </c>
+      <c r="B178" t="s">
+        <v>179</v>
+      </c>
+      <c r="C178">
+        <v>250</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:C33" xr:uid="{14B8BA79-486A-4311-9DC6-50AF49FF2C77}"/>
